--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -466,9 +466,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[奶霧灰]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HGI03023-GY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,9 +493,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[黑色]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -496,9 +520,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[燕麥白]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -511,9 +547,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -526,9 +574,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -541,9 +601,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -556,9 +628,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -571,9 +655,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -586,9 +682,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,249 +455,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,L</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[奶霧灰]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HGI03023-GY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,M</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[黑色]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HGI03023-BK</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>123::123::123</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[燕麥白]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HGI03023-WH</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::白色::XL ➜建議80-85KG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-XL</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::米咖色, M</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, XL ➜建議80-85KG</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,51 @@
           <t>主貨號</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,L</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,L</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,M</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,L</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>蝦皮</t>
+          <t>露天</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -473,12 +473,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,L</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>蝦皮</t>
+          <t>露天</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -488,17 +488,62 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,M</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>蝦皮</t>
+          <t>露天</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,6 +545,51 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,L</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>露天</t>
+          <t>蝦皮</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -473,12 +473,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,L</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>露天</t>
+          <t>蝦皮</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -488,12 +488,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,M</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>露天</t>
+          <t>蝦皮</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -548,12 +548,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>官網</t>
+          <t>露天</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -563,12 +563,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>官網</t>
+          <t>露天</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -578,12 +578,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>官網</t>
+          <t>露天</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,6 +590,51 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -466,9 +466,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[燕麥白]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,9 +493,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -496,9 +520,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色M]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -511,9 +547,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[燕麥白]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -526,9 +574,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -541,9 +601,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱[小號24L]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HGI03024-24L</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -556,9 +628,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱[特大100L]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HGI03024-100L</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -571,9 +655,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱[大號55L]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HGI03024-55L</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -586,9 +682,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤[條紋L]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-L</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -601,9 +709,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤[條紋M]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-M</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -616,9 +736,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱[特大100L]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HGI03024-100L</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -631,9 +763,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤[白色F]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HFA01022-WH-F</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,6 +500,96 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,6 +590,51 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -466,9 +466,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[奶霧灰]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HGI03023-GY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,9 +493,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[燕麥白]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -496,9 +520,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[黑色]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -511,9 +547,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -526,9 +574,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -541,9 +601,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -556,9 +628,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -571,9 +655,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤[白色F]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HFA01022-WH-F</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -586,9 +682,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤[深海藍F]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HFA01022-BU-F</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -601,9 +709,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤[條紋M]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-M</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -616,9 +736,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -631,9 +763,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>翻領插肩袖寬鬆中長版短袖T恤[杏拼黑F]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HFA01020-BGBK-F</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HFA01020</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,330 +455,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,L</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[奶霧灰]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HGI03023-GY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,L</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[燕麥白]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HGI03023-WH</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,M</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[黑色]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HGI03023-BK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>美式復古渡假風純棉短袖T恤[白色F]</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HFA01022-WH-F</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>HFA01022</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>美式復古渡假風純棉短袖T恤[深海藍F]</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HFA01022-BU-F</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HFA01022</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>美式復古寬鬆雲彩棉條紋短袖T恤[條紋M]</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HFA01021-ST-M</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HFA01021</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>翻領插肩袖寬鬆中長版短袖T恤[杏拼黑F]</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HFA01020-BGBK-F</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HFA01020</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,51 @@
           <t>主貨號</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,L</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,L</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,M</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,6 +500,51 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,6 +545,96 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -466,9 +466,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[奶霧灰]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HGI03023-GY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,9 +493,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[燕麥白]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -496,9 +520,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[黑色]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -511,9 +547,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色M]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -526,9 +574,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -541,9 +601,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -556,9 +628,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -571,9 +655,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱[中號40L]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HGI03024-40L</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -586,9 +682,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱[加大66L]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HGI03024-66L</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -601,9 +709,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱[大號55L]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HGI03024-55L</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -616,9 +736,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱[小號24L]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HGI03024-24L</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -631,9 +763,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包[白蛋色]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HGI03022-WH</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,330 +455,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,L</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[奶霧灰]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HGI03023-GY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,L</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[燕麥白]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HGI03023-WH</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,M</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[黑色]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HGI03023-BK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色M]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-M</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-XL</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>天山棉麻衣物整理摺疊收納箱[中號40L]</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HGI03024-40L</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>HGI03024</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>天山棉麻衣物整理摺疊收納箱[加大66L]</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HGI03024-66L</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HGI03024</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>天山棉麻衣物整理摺疊收納箱[大號55L]</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HGI03024-55L</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HGI03024</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>天山棉麻衣物整理摺疊收納箱[小號24L]</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HGI03024-24L</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>HGI03024</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>新款PU皮立式化妝刷具旅行收納包[白蛋色]</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HGI03022-WH</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HGI03022</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -466,9 +466,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[燕麥白]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,9 +493,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[燕麥白]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -496,9 +520,21 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架[黑色]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -511,9 +547,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -526,9 +574,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -541,9 +601,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -556,9 +628,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -571,9 +655,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色M]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -586,9 +682,21 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -601,9 +709,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -616,9 +736,21 @@
           <t>官網</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,318 +455,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,L</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[燕麥白]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HGI03023-WH</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,L</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[燕麥白]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HGI03023-WH</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,M</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架[黑色]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HGI03023-BK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-XL</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-XL</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色M]</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-M</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-XL</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-XL</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E468"/>
+  <dimension ref="A1:E480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7246,21 +7246,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>HME03001-PB-L</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="inlineStr"/>
+      <c r="E454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -7273,21 +7261,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>HME03001-DN-L</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -7300,21 +7276,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>HME03001-BK-L</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="inlineStr"/>
+      <c r="E456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -7327,21 +7291,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>HME03001-WH-L</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="inlineStr"/>
+      <c r="E457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -7354,21 +7306,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>HME03001-BR-L</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="inlineStr"/>
+      <c r="E458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -7381,21 +7321,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色XL]</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>HME03001-PB-XL</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr"/>
+      <c r="E459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -7408,21 +7336,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>HME03001-BR-XL</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr"/>
+      <c r="E460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -7435,21 +7351,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>HME03001-RD-XL</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="inlineStr"/>
+      <c r="E461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -7462,21 +7366,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>HME03001-DN-XL</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr"/>
+      <c r="E462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -7489,21 +7381,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>HME03001-PU-XL</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr"/>
+      <c r="E463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -7516,21 +7396,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>HME03001-GY-XL</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr"/>
+      <c r="E464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -7543,21 +7411,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[白色XL]</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>HME03001-WH-XL</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C465" t="inlineStr"/>
+      <c r="D465" t="inlineStr"/>
+      <c r="E465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -7570,21 +7426,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>未匹配</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>HFA02001-WH_TN-L</t>
-        </is>
-      </c>
-      <c r="E466" t="inlineStr">
-        <is>
-          <t>HFA02001</t>
-        </is>
-      </c>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="inlineStr"/>
+      <c r="E466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -7597,21 +7441,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>未匹配</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>HFA02001-WH_CN-L</t>
-        </is>
-      </c>
-      <c r="E467" t="inlineStr">
-        <is>
-          <t>HFA02001</t>
-        </is>
-      </c>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -7624,19 +7456,331 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>素色冰絲女士三角內褲[白色L]</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>HFE03001-WH-L</t>
-        </is>
-      </c>
-      <c r="E468" t="inlineStr">
-        <is>
-          <t>HFE03001</t>
+      <c r="C468" t="inlineStr"/>
+      <c r="D468" t="inlineStr"/>
+      <c r="E468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色M]</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>HME03001-WH-M</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::灰色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色M]</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>HME03001-RD-M</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::藏藍色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, M</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M]</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>HFE03002-GN-M</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::紫羅蘭, M</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭M]</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>HFE03002-PU-M</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::煙粉色, M</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[煙粉色M]</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>HFE03002-PK-M</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::米咖色, M</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[米咖色M]</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>HFE03002-BG-M</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>HME03002</t>
         </is>
       </c>
     </row>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E779"/>
+  <dimension ref="A1:E781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12121,17 +12121,59 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色S]</t>
-        </is>
-      </c>
-      <c r="D779" t="inlineStr">
-        <is>
-          <t>HME03001-BK-S</t>
-        </is>
-      </c>
-      <c r="E779" t="inlineStr">
+      <c r="C779" t="inlineStr"/>
+      <c r="D779" t="inlineStr"/>
+      <c r="E779" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, M</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M]</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>HFE03002-GN-M</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色XL]</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>HME03001-BK-XL</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
         <is>
           <t>HME03001</t>
         </is>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHIEMI 寬鬆五分袖T恤裙｜韓系街頭風 NO字母印花 中性連衣裙 洋裝 連身裙 三色可選::灰色,F</t>
+          <t>::</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKEA 正版環保購物袋 71公升 76公升 現貨代購｜洗衣袋 藍色提袋 媽媽包 購物袋 收納袋 手提袋 收納袋 大容量::【手提款】71L ➜55x37x35cm</t>
+          <t>CHIEMI 寬鬆五分袖T恤裙｜韓系街頭風 NO字母印花 中性連衣裙 洋裝 連身裙 三色可選::灰色,F</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::淺卡其｜圓領,XL</t>
+          <t>IKEA 正版環保購物袋 71公升 76公升 現貨代購｜洗衣袋 藍色提袋 媽媽包 購物袋 收納袋 手提袋 收納袋 大容量::【手提款】71L ➜55x37x35cm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::淺卡其｜立領,M</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::淺卡其｜圓領,XL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::淺卡其｜立領,XL</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::淺卡其｜立領,M</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::淺卡其｜高領,M</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::淺卡其｜立領,XL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::淺卡其｜高領,S</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::淺卡其｜高領,M</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::灰色｜圓領,L</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::淺卡其｜高領,S</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -578,7 +578,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::灰色｜立領,M</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::灰色｜圓領,L</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::灰色｜立領,XL</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::灰色｜立領,M</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::灰色｜高領,L</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::灰色｜立領,XL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::灰色｜高領,XL</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::灰色｜高領,L</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -638,7 +638,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜圓領,S</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::灰色｜高領,XL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜圓領,XL</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜圓領,S</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜立領,L</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜圓領,XL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜立領,M</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜立領,L</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -698,7 +698,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜立領,S</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜立領,M</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜立領,XL</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜立領,S</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜高領,L</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜立領,XL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜高領,M</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜高領,L</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜高領,S</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜高領,M</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜高領,XL</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜高領,S</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -788,7 +788,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::粉色｜立領,L</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::白色｜高領,XL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::粉色｜立領,M</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::粉色｜立領,L</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::粉色｜高領,L</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::粉色｜立領,M</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::粉色｜高領,M</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::粉色｜高領,L</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -848,7 +848,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::霧藍色｜圓領,L</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::粉色｜高領,M</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::霧藍色｜立領,M</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::霧藍色｜圓領,L</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::霧藍色｜立領,XL</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::霧藍色｜立領,M</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜圓領,L</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::霧藍色｜立領,XL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -908,7 +908,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜圓領,S</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜圓領,L</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜圓領,XL</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜圓領,S</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -938,7 +938,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜立領,L</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜圓領,XL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -953,7 +953,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜立領,M</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜立領,L</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -968,7 +968,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜立領,S</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜立領,M</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜立領,XL</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜立領,S</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -998,7 +998,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜高領,L</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜立領,XL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜高領,M</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜高領,L</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1028,7 +1028,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜高領,S</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜高領,M</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1043,7 +1043,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜高領,XL</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜高領,S</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1058,7 +1058,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::奶奶灰,L</t>
+          <t>[CHIEMI]內搭長袖 高領打底衣 立領上衣 內搭上衣 高領內搭 圓領 半高領 小立領 冬天 長袖 薄::黑色｜高領,XL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::奶奶灰,M</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::奶奶灰,L</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::奶奶灰,XL</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::奶奶灰,M</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::寶寶藍,L</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::奶奶灰,XL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1118,7 +1118,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::寶寶藍,M</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::寶寶藍,L</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::摩卡色,L</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::寶寶藍,M</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1148,7 +1148,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::摩卡色,XL</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::摩卡色,L</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::燕麥米,L</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::摩卡色,XL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1178,7 +1178,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::燕麥米,M</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::燕麥米,L</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::燕麥米,XL</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::燕麥米,M</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1208,7 +1208,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::白色,L</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::燕麥米,XL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::白色,XL</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::白色,L</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1238,7 +1238,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::黑色,L</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::白色,XL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1253,7 +1253,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::黑色,XL</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::黑色,L</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1268,7 +1268,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::卡其色</t>
+          <t>[CHIEMI]打底衫 針織衫 打底衣 內搭上衣 內搭長袖 半高領 小立領 冬天 女::黑色,XL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::咖啡色</t>
+          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::卡其色</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1298,7 +1298,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::淺灰色</t>
+          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::咖啡色</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::白色</t>
+          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::淺灰色</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1328,7 +1328,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::藕紫色</t>
+          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::白色</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::黑色</t>
+          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::藕紫色</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,L ➜建議70-75KG</t>
+          <t>[CHIEMI]羊絨襪 羊毛襪 毛襪 發熱襪 保暖襪 女 隔日配 隔日到貨::黑色</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1373,7 +1373,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,M ➜建議60-65KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1388,7 +1388,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,S ➜建議50-55KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,XL ➜建議80-85KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,L ➜建議70-75KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1433,7 +1433,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,M ➜建議60-65KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1448,7 +1448,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,S ➜建議50-55KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,XL ➜建議80-85KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1478,7 +1478,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::灰色,L ➜建議70-75KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::灰色,M ➜建議60-65KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::灰色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1508,7 +1508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::灰色,S ➜建議50-55KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::灰色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::灰色,XL ➜建議80-85KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::灰色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::白色,L ➜建議70-75KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::灰色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::白色,M ➜建議60-65KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::白色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::白色,S ➜建議50-55KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::白色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1583,7 +1583,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::白色,XL ➜建議80-85KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::白色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1598,7 +1598,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::紫色,L ➜建議70-75KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::白色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1613,7 +1613,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::紫色,M ➜建議60-65KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::紫色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::紫色,S ➜建議50-55KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::紫色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::紫色,XL ➜建議80-85KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::紫色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,L ➜建議70-75KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::紫色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,M ➜建議60-65KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1688,7 +1688,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,S ➜建議50-55KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,XL ➜建議80-85KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1718,7 +1718,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,L ➜建議70-75KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,M ➜建議60-65KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1748,7 +1748,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,S ➜建議50-55KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,XL ➜建議80-85KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1778,7 +1778,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::黑色,L ➜建議70-75KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1793,7 +1793,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::黑色,M ➜建議60-65KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::黑色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::黑色,S ➜建議50-55KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::黑色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::黑色,XL ➜建議80-85KG</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::黑色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1838,7 +1838,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>[MIT獨家訂製✨白皮美肌色]絲襪 褲襪 透膚絲襪 黑絲襪 膚色絲襪::基本黑</t>
+          <t>[CHIEMI🏆銷售冠軍]冰絲內褲 男內褲 內褲男 男性內褲::黑色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1853,7 +1853,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>[MIT獨家訂製✨白皮美肌色]絲襪 褲襪 透膚絲襪 黑絲襪 膚色絲襪::白皙膚</t>
+          <t>[MIT獨家訂製✨白皮美肌色]絲襪 褲襪 透膚絲襪 黑絲襪 膚色絲襪::基本黑</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1868,7 +1868,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>[MIT獨家訂製✨白皮美肌色]絲襪 褲襪 透膚絲襪 黑絲襪 膚色絲襪::自然膚</t>
+          <t>[MIT獨家訂製✨白皮美肌色]絲襪 褲襪 透膚絲襪 黑絲襪 膚色絲襪::白皙膚</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1883,7 +1883,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::丁香紫,L</t>
+          <t>[MIT獨家訂製✨白皮美肌色]絲襪 褲襪 透膚絲襪 黑絲襪 膚色絲襪::自然膚</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1898,7 +1898,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::丁香紫,M</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::丁香紫,L</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1913,7 +1913,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::丁香紫,XL</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::丁香紫,M</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1928,7 +1928,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::中豆紅,L</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::丁香紫,XL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1943,7 +1943,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::中豆紅,M</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::中豆紅,L</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1958,7 +1958,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::中豆紅,XL</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::中豆紅,M</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::白色,L</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::中豆紅,XL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1988,7 +1988,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::白色,M</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::白色,L</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::白色,XL</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::白色,M</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2018,7 +2018,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::膚色,L</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::白色,XL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2033,7 +2033,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::膚色,M</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::膚色,L</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2048,7 +2048,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::膚色,XL</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::膚色,M</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2063,7 +2063,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::藍灰色,L</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::膚色,XL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::藍灰色,M</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::藍灰色,L</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2093,7 +2093,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::藍灰色,XL</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::藍灰色,M</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2108,7 +2108,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::黑色,L</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::藍灰色,XL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::黑色,M</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::黑色,L</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2138,7 +2138,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::黑色,XL</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::黑色,M</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2153,7 +2153,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>[V領修臉✅春夏打底]內搭上衣 莫代爾上衣 v領上衣 白色黑色 素色 t恤 v領 t恤::咖啡色,M</t>
+          <t>[SGS安全認證🏆五星好評爆賣𝟏𝟎萬件] 冰絲內褲 中腰內褲 無痕內褲  女生內褲 女內褲::黑色,XL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2168,7 +2168,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>[V領修臉✅春夏打底]內搭上衣 莫代爾上衣 v領上衣 白色黑色 素色 t恤 v領 t恤::咖啡色,XL</t>
+          <t>[V領修臉✅春夏打底]內搭上衣 莫代爾上衣 v領上衣 白色黑色 素色 t恤 v領 t恤::咖啡色,M</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2183,7 +2183,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>[V領修臉✅春夏打底]內搭上衣 莫代爾上衣 v領上衣 白色黑色 素色 t恤 v領 t恤::白色,XL</t>
+          <t>[V領修臉✅春夏打底]內搭上衣 莫代爾上衣 v領上衣 白色黑色 素色 t恤 v領 t恤::咖啡色,XL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2198,7 +2198,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>[V領修臉✅春夏打底]內搭上衣 莫代爾上衣 v領上衣 白色黑色 素色 t恤 v領 t恤::黑色,L</t>
+          <t>[V領修臉✅春夏打底]內搭上衣 莫代爾上衣 v領上衣 白色黑色 素色 t恤 v領 t恤::白色,XL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2213,7 +2213,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>[一件式懶人穿搭💙百搭寬鬆直筒] 長版T恤 長版上衣 短袖洋裝 休閒洋裝 孕婦裝夏天 顯瘦洋裝::黑色,F</t>
+          <t>[V領修臉✅春夏打底]內搭上衣 莫代爾上衣 v領上衣 白色黑色 素色 t恤 v領 t恤::黑色,L</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>[三格收納🌟桌面雜亂小幫手]桌面收納盒 筆筒 桌面收納 辦公桌收納 桌上收納盒 桌上收納::粉色,約13.2x8x12.7cm</t>
+          <t>[一件式懶人穿搭💙百搭寬鬆直筒] 長版T恤 長版上衣 短袖洋裝 休閒洋裝 孕婦裝夏天 顯瘦洋裝::黑色,F</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>[三格收納🌟桌面雜亂小幫手]桌面收納盒 筆筒 桌面收納 辦公桌收納 桌上收納盒 桌上收納::藍色,約13.2x8x12.7cm</t>
+          <t>[三格收納🌟桌面雜亂小幫手]桌面收納盒 筆筒 桌面收納 辦公桌收納 桌上收納盒 桌上收納::粉色,約13.2x8x12.7cm</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2258,7 +2258,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>[免穿內衣🤍居家必備]bratop 內搭背心 胸墊背心 細肩帶背心 brotop 背心::夜空黑,L</t>
+          <t>[三格收納🌟桌面雜亂小幫手]桌面收納盒 筆筒 桌面收納 辦公桌收納 桌上收納盒 桌上收納::藍色,約13.2x8x12.7cm</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2273,7 +2273,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>[免穿內衣🤍居家必備]bratop 內搭背心 胸墊背心 細肩帶背心 brotop 背心::霧霾藍,M</t>
+          <t>[免穿內衣🤍居家必備]bratop 內搭背心 胸墊背心 細肩帶背心 brotop 背心::夜空黑,L</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2288,7 +2288,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>[免釘無痕・不傷牆面]無痕掛勾 掛勾 掛鉤 門後掛鉤 門後掛勾 廚房掛勾 貼片 強力 置物架 無痕::白色</t>
+          <t>[免穿內衣🤍居家必備]bratop 內搭背心 胸墊背心 細肩帶背心 brotop 背心::霧霾藍,M</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2303,7 +2303,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>[免釘無痕・不傷牆面]無痕掛勾 掛勾 掛鉤 門後掛鉤 門後掛勾 廚房掛勾 貼片 強力 置物架 無痕::米黃色</t>
+          <t>[免釘無痕・不傷牆面]無痕掛勾 掛勾 掛鉤 門後掛鉤 門後掛勾 廚房掛勾 貼片 強力 置物架 無痕::白色</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2318,7 +2318,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::原味黑糖塊,單顆入（一顆淨重約18g）</t>
+          <t>[免釘無痕・不傷牆面]無痕掛勾 掛勾 掛鉤 門後掛鉤 門後掛勾 廚房掛勾 貼片 強力 置物架 無痕::米黃色</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2333,7 +2333,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::桂圓紅棗黑糖塊,單顆入（一顆淨重約18g）</t>
+          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::原味黑糖塊,單顆入（一顆淨重約18g）</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2348,7 +2348,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::桂花黑糖塊,單顆入（一顆淨重約18g）</t>
+          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::桂圓紅棗黑糖塊,單顆入（一顆淨重約18g）</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::海燕窩黑糖塊,單顆入（一顆淨重約18g）</t>
+          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::桂花黑糖塊,單顆入（一顆淨重約18g）</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2378,7 +2378,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::玫瑰四物黑糖塊,單顆入（一顆淨重約18g）</t>
+          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::海燕窩黑糖塊,單顆入（一顆淨重約18g）</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2393,7 +2393,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::老薑黑糖塊,單顆入（一顆淨重約18g）</t>
+          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::玫瑰四物黑糖塊,單顆入（一顆淨重約18g）</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2408,7 +2408,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::中灰色,L</t>
+          <t>[冬天不靠男友💪靠黑糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::老薑黑糖塊,單顆入（一顆淨重約18g）</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::深灰色,L</t>
+          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::中灰色,L</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2438,7 +2438,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::深灰色,M</t>
+          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::深灰色,L</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2453,7 +2453,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::深灰色,XL</t>
+          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::深灰色,M</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2468,7 +2468,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::黑色,L</t>
+          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::深灰色,XL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2483,7 +2483,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::黑色,M</t>
+          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::黑色,L</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::黑色,XL</t>
+          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::黑色,M</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::咖啡色,M</t>
+          <t>[冬天也能穿出S曲線]微喇叭褲 保暖褲 刷毛喇叭褲 鯊魚褲 加絨長褲 保暖長褲 緊身褲 加絨 刷毛 冬天 冬 內裡刷毛::黑色,XL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2528,7 +2528,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::咖啡色,XL</t>
+          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::咖啡色,M</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::深灰色,L</t>
+          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::咖啡色,XL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2558,7 +2558,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::深灰色,M</t>
+          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::深灰色,L</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2573,7 +2573,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::深灰色,XL</t>
+          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::深灰色,M</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2588,7 +2588,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::米白色,L</t>
+          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::深灰色,XL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2603,7 +2603,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::米白色,M</t>
+          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::米白色,L</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2618,7 +2618,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::米白色,XL</t>
+          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::米白色,M</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2633,7 +2633,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>[剛剛好的微短不露肚]短版t恤 女生上衣 短版上衣女 上衣女短袖 短板::杏色,XL</t>
+          <t>[冬季萌系裙🤍防走光更放心]毛呢短裙 百褶裙 超短裙 秋冬短裙 冬天短裙::米白色,XL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>[剛剛好的微短不露肚]短版t恤 女生上衣 短版上衣女 上衣女短袖 短板::深藍,XL</t>
+          <t>[剛剛好的微短不露肚]短版t恤 女生上衣 短版上衣女 上衣女短袖 短板::杏色,XL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::卡其色｜襪套❌非襪子</t>
+          <t>[剛剛好的微短不露肚]短版t恤 女生上衣 短版上衣女 上衣女短袖 短板::深藍,XL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2678,7 +2678,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::咖啡色｜襪套❌非襪子</t>
+          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::卡其色｜襪套❌非襪子</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2693,7 +2693,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::奶白色｜襪套❌非襪子</t>
+          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::咖啡色｜襪套❌非襪子</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2708,7 +2708,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::深灰色｜襪套❌非襪子</t>
+          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::奶白色｜襪套❌非襪子</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2723,7 +2723,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::淺灰色｜襪套❌非襪子</t>
+          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::深灰色｜襪套❌非襪子</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2738,7 +2738,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::淺粉色｜襪套❌非襪子</t>
+          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::淺灰色｜襪套❌非襪子</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2753,7 +2753,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::白色｜襪套❌非襪子</t>
+          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::淺粉色｜襪套❌非襪子</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2768,7 +2768,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::黑色｜襪套❌非襪子</t>
+          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::白色｜襪套❌非襪子</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2783,7 +2783,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,L ➜建議70-75KG</t>
+          <t>[可愛泡泡襪套．瘦腿小心機]堆堆襪套 襪套 保暖襪套 堆堆襪腿套 堆堆襪 泡泡襪套 泡泡襪 長筒襪 保暖 冬天 襪子 女::黑色｜襪套❌非襪子</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2798,7 +2798,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,M ➜建議60-65KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2813,7 +2813,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,S ➜建議50-55KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2828,7 +2828,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,L ➜建議70-75KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::咖啡色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2858,7 +2858,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,M ➜建議60-65KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,S ➜建議50-55KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2888,7 +2888,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2903,7 +2903,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::灰色,L ➜建議70-75KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::寶藍色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::灰色,M ➜建議60-65KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::灰色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::灰色,S ➜建議50-55KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::灰色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2948,7 +2948,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::灰色,XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::灰色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2963,7 +2963,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::白色,L ➜建議70-75KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::灰色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::白色,M ➜建議60-65KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::白色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2993,7 +2993,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::白色,S ➜建議50-55KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::白色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3008,7 +3008,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::白色,XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::白色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::紫色,L ➜建議70-75KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::白色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3038,7 +3038,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::紫色,M ➜建議60-65KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::紫色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3053,7 +3053,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::紫色,S ➜建議50-55KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::紫色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3068,7 +3068,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::紫色,XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::紫色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,L ➜建議70-75KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::紫色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3098,7 +3098,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,M ➜建議60-65KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3113,7 +3113,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,S ➜建議50-55KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3128,7 +3128,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3143,7 +3143,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,L ➜建議70-75KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::藏藍色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3158,7 +3158,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,M ➜建議60-65KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3173,7 +3173,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3188,7 +3188,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::黑色,L ➜建議70-75KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::酒紅色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3203,7 +3203,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::黑色,M ➜建議60-65KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::黑色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3218,7 +3218,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::黑色,S ➜建議50-55KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::黑色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3233,7 +3233,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::黑色,XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::黑色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3248,7 +3248,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【平口款】灰色,F（男女通用）</t>
+          <t>[台灣冠軍🏆𝟏𝟎件𝟗折]冰絲內褲 男內褲 內褲男 男性內褲::黑色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3263,7 +3263,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【平口款】藏藍色,F（男女通用）</t>
+          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【平口款】灰色,F（男女通用）</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3278,7 +3278,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【平口款】黑色,F（男女通用）</t>
+          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【平口款】藏藍色,F（男女通用）</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【露指款】灰色,F（男女通用）</t>
+          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【平口款】黑色,F（男女通用）</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3308,7 +3308,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【露指款】藏藍色,F（男女通用）</t>
+          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【露指款】灰色,F（男女通用）</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3323,7 +3323,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【露指款】黑色,F（男女通用）</t>
+          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【露指款】藏藍色,F（男女通用）</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3338,7 +3338,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::亮膚色,140克刷毛款❄️推薦冬日.ᐟ不透膚</t>
+          <t>[台灣製涼感紗🧊機車族必備]防曬袖套 袖套 涼感袖套 冰絲袖套 運動袖套 手袖::【露指款】黑色,F（男女通用）</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3353,7 +3353,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::亮膚色,30克超薄透絲襪☀️夏日著用.ᐟ半透膚</t>
+          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::亮膚色,140克刷毛款❄️推薦冬日.ᐟ不透膚</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3368,7 +3368,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::亮膚色,50克無絨薄款🍂推薦春秋.ᐟ不透膚</t>
+          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::亮膚色,30克超薄透絲襪☀️夏日著用.ᐟ半透膚</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3383,7 +3383,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::深膚色,140克刷毛款❄️推薦冬日.ᐟ不透膚</t>
+          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::亮膚色,50克無絨薄款🍂推薦春秋.ᐟ不透膚</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::深膚色,30克超薄透絲襪☀️夏日著用.ᐟ半透膚</t>
+          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::深膚色,140克刷毛款❄️推薦冬日.ᐟ不透膚</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3413,7 +3413,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::深膚色,50克無絨薄款🍂推薦春秋.ᐟ不透膚</t>
+          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::深膚色,30克超薄透絲襪☀️夏日著用.ᐟ半透膚</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3428,7 +3428,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::黑色,140克刷毛款❄️推薦冬日.ᐟ不透膚</t>
+          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::深膚色,50克無絨薄款🍂推薦春秋.ᐟ不透膚</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::黑色,30克超薄透絲襪☀️夏日著用.ᐟ半透膚</t>
+          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::黑色,140克刷毛款❄️推薦冬日.ᐟ不透膚</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3458,7 +3458,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::黑色,50克無絨薄款🍂推薦春秋.ᐟ不透膚</t>
+          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::黑色,30克超薄透絲襪☀️夏日著用.ᐟ半透膚</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3473,7 +3473,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶中長版,L</t>
+          <t>[台灣製高品質🇹🇼夏薄冬暖一次搞定]褲襪 絲襪 刷毛褲襪 透膚絲襪 黑絲襪 膚色絲襪::黑色,50克無絨薄款🍂推薦春秋.ᐟ不透膚</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3488,7 +3488,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶中長版,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶中長版,L</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3503,7 +3503,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶中長版,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶中長版,M</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3518,7 +3518,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶加長版,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶中長版,XL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3533,7 +3533,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶短版,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶加長版,XL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3548,7 +3548,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶短版,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶短版,L</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3563,7 +3563,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶短版,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶短版,M</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3578,7 +3578,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶中長版 ❗️微透❗️,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【灰色】吊帶款▶短版,XL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3593,7 +3593,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶中長版 ❗️微透❗️,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶中長版 ❗️微透❗️,L</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶中長版 ❗️微透❗️,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶中長版 ❗️微透❗️,M</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -3623,7 +3623,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶加長版 ❗️微透❗️,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶中長版 ❗️微透❗️,XL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶加長版 ❗️微透❗️,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶加長版 ❗️微透❗️,L</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -3653,7 +3653,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶短版 ❗️微透❗️,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶加長版 ❗️微透❗️,XL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3668,7 +3668,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶短版 ❗️微透❗️,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶短版 ❗️微透❗️,L</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3676,26 +3676,14 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/白色M]</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>HFC01001-TS-SH-WH-M</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>HFC01001</t>
-        </is>
-      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶短版 ❗️微透❗️,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶短版 ❗️微透❗️,M</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3703,14 +3691,26 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>莫代爾打底連身裙[吊帶款/短版/白色M]</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-SH-WH-M</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶中長版,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶短版 ❗️微透❗️,XL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3725,7 +3725,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶中長版,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶中長版,L</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3740,7 +3740,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶中長版,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶中長版,M</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3755,7 +3755,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶加長版,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶中長版,XL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3770,7 +3770,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶加長版,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶加長版,L</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3785,7 +3785,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶加長版,XL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,L</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3808,26 +3808,14 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/黑色M]</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>HFC01001-TS-SH-BK-M</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>HFC01001</t>
-        </is>
-      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,M</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3835,14 +3823,26 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>莫代爾打底連身裙[吊帶款/短版/黑色M]</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-SH-BK-M</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖灰色〗背心款▶中長版,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,XL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3857,7 +3857,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖灰色〗背心款▶中長版,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖灰色〗背心款▶中長版,L</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3872,7 +3872,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖灰色〗背心款▶中長版,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖灰色〗背心款▶中長版,M</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3887,7 +3887,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖灰色〗背心款▶短版,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖灰色〗背心款▶中長版,XL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖灰色〗背心款▶短版,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖灰色〗背心款▶短版,M</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3917,7 +3917,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶中長版 ❗️微透❗️,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖灰色〗背心款▶短版,XL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3932,7 +3932,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶中長版 ❗️微透❗️,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶中長版 ❗️微透❗️,L</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3947,7 +3947,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶中長版 ❗️微透❗️,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶中長版 ❗️微透❗️,M</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3962,7 +3962,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶短版 ❗️微透❗️,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶中長版 ❗️微透❗️,XL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3977,7 +3977,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶短版 ❗️微透❗️,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶短版 ❗️微透❗️,L</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3992,7 +3992,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶短版 ❗️微透❗️,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶短版 ❗️微透❗️,M</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -4007,7 +4007,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶中長版,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖白色〗背心款▶短版 ❗️微透❗️,XL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶中長版,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶中長版,L</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -4037,7 +4037,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶中長版,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶中長版,M</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4052,7 +4052,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,L</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶中長版,XL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,M</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,L</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4082,7 +4082,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,XL</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,M</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4097,7 +4097,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>[奶油系🧁化妝桌優雅不凌亂]化妝品收納 桌面收納 保養品收納 桌上收納盒 桌上收納::奶油白,約25x19x35cm</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::〖黑色〗背心款▶短版,XL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4112,7 +4112,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>[奶油風🧁大容量防水果凍包] 透明提袋 收納包 游泳袋 旅行收納袋 透明收納袋 防水提袋 游泳包 沙灘包::拉鍊款,米色邊</t>
+          <t>[奶油系🧁化妝桌優雅不凌亂]化妝品收納 桌面收納 保養品收納 桌上收納盒 桌上收納::奶油白,約25x19x35cm</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4127,7 +4127,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>[奶油風🧁大容量防水果凍包] 透明提袋 收納包 游泳袋 旅行收納袋 透明收納袋 防水提袋 游泳包 沙灘包::拉鍊款,黑色邊</t>
+          <t>[奶油風🧁大容量防水果凍包] 透明提袋 收納包 游泳袋 旅行收納袋 透明收納袋 防水提袋 游泳包 沙灘包::拉鍊款,米色邊</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4142,7 +4142,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>[奶油風🧁大容量防水果凍包] 透明提袋 收納包 游泳袋 旅行收納袋 透明收納袋 防水提袋 游泳包 沙灘包::鈕釦款,米色邊</t>
+          <t>[奶油風🧁大容量防水果凍包] 透明提袋 收納包 游泳袋 旅行收納袋 透明收納袋 防水提袋 游泳包 沙灘包::拉鍊款,黑色邊</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4157,7 +4157,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::原味黑糖塊,【罐裝】400g</t>
+          <t>[奶油風🧁大容量防水果凍包] 透明提袋 收納包 游泳袋 旅行收納袋 透明收納袋 防水提袋 游泳包 沙灘包::鈕釦款,米色邊</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4172,7 +4172,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::桂花黑糖塊,【罐裝】400g</t>
+          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::原味黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::海燕窩黑糖塊,【罐裝】400g</t>
+          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::桂花黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::玫瑰四物黑糖塊,【罐裝】400g</t>
+          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::海燕窩黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4217,7 +4217,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::紅棗桂圓黑糖塊,【罐裝】400g</t>
+          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::玫瑰四物黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4232,7 +4232,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::老薑黑糖塊,【罐裝】400g</t>
+          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::紅棗桂圓黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4247,7 +4247,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜中領,L</t>
+          <t>[實惠罐裝_每一顆都好糖]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶::老薑黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4262,7 +4262,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜中領,S</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜中領,L</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4277,7 +4277,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜中領,XL</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜中領,S</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4292,7 +4292,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜圓領,L</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜中領,XL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜圓領,M</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜圓領,L</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4322,7 +4322,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜圓領,XL</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜圓領,M</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4337,7 +4337,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::珊瑚粉｜中領,M</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::月光灰｜圓領,XL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::珊瑚粉｜中領,XL</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::珊瑚粉｜中領,M</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4367,7 +4367,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::珊瑚粉｜圓領,M</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::珊瑚粉｜中領,XL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4382,7 +4382,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::珊瑚粉｜圓領,S</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::珊瑚粉｜圓領,M</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4397,7 +4397,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜中領,L</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::珊瑚粉｜圓領,S</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4412,7 +4412,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜中領,M</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜中領,L</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4427,7 +4427,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜中領,S</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜中領,M</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4442,7 +4442,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜中領,XL</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜中領,S</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4457,7 +4457,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜圓領,L</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜中領,XL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4472,7 +4472,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜圓領,S</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜圓領,L</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4487,7 +4487,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜圓領,XL</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜圓領,S</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4502,7 +4502,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::經典膚｜中領,S</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::神秘黑｜圓領,XL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -4517,7 +4517,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::經典膚｜中領,XL</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::經典膚｜中領,S</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4532,7 +4532,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::經典膚｜圓領,L</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::經典膚｜中領,XL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -4547,7 +4547,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::經典膚｜圓領,M</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::經典膚｜圓領,L</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -4562,7 +4562,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>[情侶一起穿✨日常百搭款]大學t長袖 長袖上衣女 長袖t恤女 大學t 女 衛衣::沙粉色,M ➜建議50-65KG｜推薦女穿</t>
+          <t>[德絨軟糯好穿☃️圓領/高領自由選]德絨打底衫 打底衣 高領打底衣 內搭衣 高領內搭 內搭長袖::經典膚｜圓領,M</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4577,7 +4577,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>[情侶一起穿✨日常百搭款]大學t長袖 長袖上衣女 長袖t恤女 大學t 女 衛衣::黑色,M ➜建議50-65KG｜推薦女穿</t>
+          <t>[情侶一起穿✨日常百搭款]大學t長袖 長袖上衣女 長袖t恤女 大學t 女 衛衣::沙粉色,M ➜建議50-65KG｜推薦女穿</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4592,7 +4592,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>[情侶一起穿✨日常百搭款]大學t長袖 長袖上衣女 長袖t恤女 大學t 女 衛衣::黑色,S ➜建議40-50KG｜推薦女穿</t>
+          <t>[情侶一起穿✨日常百搭款]大學t長袖 長袖上衣女 長袖t恤女 大學t 女 衛衣::黑色,M ➜建議50-65KG｜推薦女穿</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -4607,7 +4607,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>[情侶款珊瑚絨睡衣套裝]情侶睡衣 睡衣套裝 毛絨睡衣 珊瑚絨睡衣 冬季睡衣 冬天睡衣 保暖睡衣::【女款】米白色</t>
+          <t>[情侶一起穿✨日常百搭款]大學t長袖 長袖上衣女 長袖t恤女 大學t 女 衛衣::黑色,S ➜建議40-50KG｜推薦女穿</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -4622,7 +4622,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>[情侶款珊瑚絨睡衣套裝]情侶睡衣 睡衣套裝 毛絨睡衣 珊瑚絨睡衣 冬季睡衣 冬天睡衣 保暖睡衣::【男款】深灰色</t>
+          <t>[情侶款珊瑚絨睡衣套裝]情侶睡衣 睡衣套裝 毛絨睡衣 珊瑚絨睡衣 冬季睡衣 冬天睡衣 保暖睡衣::【女款】米白色</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4637,7 +4637,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【灰色】細肩帶,M</t>
+          <t>[情侶款珊瑚絨睡衣套裝]情侶睡衣 睡衣套裝 毛絨睡衣 珊瑚絨睡衣 冬季睡衣 冬天睡衣 保暖睡衣::【男款】深灰色</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【白色】細肩帶,L</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【灰色】細肩帶,M</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4667,7 +4667,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【白色】細肩帶,M</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【白色】細肩帶,L</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4682,7 +4682,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【膚色】細肩帶,L</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【白色】細肩帶,M</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -4697,7 +4697,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【膚色】細肩帶,M</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【膚色】細肩帶,L</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【黑色】細肩帶,L</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【膚色】細肩帶,M</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4727,7 +4727,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【黑色】細肩帶,M</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【黑色】細肩帶,L</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4742,7 +4742,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖灰色〗寬肩帶,L</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::【黑色】細肩帶,M</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -4757,7 +4757,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖白色〗寬肩帶,L</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖灰色〗寬肩帶,L</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -4772,7 +4772,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖白色〗寬肩帶,M</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖白色〗寬肩帶,L</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4787,7 +4787,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖膚色〗寬肩帶,L</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖白色〗寬肩帶,M</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖膚色〗寬肩帶,M</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖膚色〗寬肩帶,L</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4817,7 +4817,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖黑色〗寬肩帶,L</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖膚色〗寬肩帶,M</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4832,7 +4832,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖黑色〗寬肩帶,M</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖黑色〗寬肩帶,L</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>[整理師大推👍換季收納好幫手]衣服收納箱 棉被收納袋 衣物收納 衣服收納袋 衣物收納箱::加大66L</t>
+          <t>[打底專用☁️輕薄滑順] 莫代爾背心 內襯衣  女生背心 細肩背心 小可愛::〖黑色〗寬肩帶,M</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -4862,7 +4862,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>[整理師大推👍換季收納好幫手]衣服收納箱 棉被收納袋 衣物收納 衣服收納袋 衣物收納箱::小號24L</t>
+          <t>[整理師大推👍換季收納好幫手]衣服收納箱 棉被收納袋 衣物收納 衣服收納袋 衣物收納箱::加大66L</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -4877,7 +4877,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>[整理師大推👍換季收納好幫手]衣服收納箱 棉被收納袋 衣物收納 衣服收納袋 衣物收納箱::特大100L</t>
+          <t>[整理師大推👍換季收納好幫手]衣服收納箱 棉被收納袋 衣物收納 衣服收納袋 衣物收納箱::小號24L</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -4892,7 +4892,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>[新品上市🎁贈可拆卸肩帶]無肩帶內衣 平口內衣 抹胸 隱形內衣 胸罩 小胸內衣::乳白色,L｜推薦80A/80B</t>
+          <t>[整理師大推👍換季收納好幫手]衣服收納箱 棉被收納袋 衣物收納 衣服收納袋 衣物收納箱::特大100L</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>[新品上市🎁贈可拆卸肩帶]無肩帶內衣 平口內衣 抹胸 隱形內衣 胸罩 小胸內衣::乳白色,S｜推薦70A/70B</t>
+          <t>[新品上市🎁贈可拆卸肩帶]無肩帶內衣 平口內衣 抹胸 隱形內衣 胸罩 小胸內衣::乳白色,L｜推薦80A/80B</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>[新品上市🎁贈可拆卸肩帶]無肩帶內衣 平口內衣 抹胸 隱形內衣 胸罩 小胸內衣::優雅黑,L｜推薦80A/80B</t>
+          <t>[新品上市🎁贈可拆卸肩帶]無肩帶內衣 平口內衣 抹胸 隱形內衣 胸罩 小胸內衣::乳白色,S｜推薦70A/70B</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4937,7 +4937,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>[新品上市🎁贈可拆卸肩帶]無肩帶內衣 平口內衣 抹胸 隱形內衣 胸罩 小胸內衣::粉底膚,S｜推薦70A/70B</t>
+          <t>[新品上市🎁贈可拆卸肩帶]無肩帶內衣 平口內衣 抹胸 隱形內衣 胸罩 小胸內衣::優雅黑,L｜推薦80A/80B</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -4952,7 +4952,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>[新品上市🎁贈可拆卸肩帶]無肩帶內衣 平口內衣 抹胸 隱形內衣 胸罩 小胸內衣::高級灰,L｜推薦80A/80B</t>
+          <t>[新品上市🎁贈可拆卸肩帶]無肩帶內衣 平口內衣 抹胸 隱形內衣 胸罩 小胸內衣::粉底膚,S｜推薦70A/70B</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -4967,7 +4967,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::冰川白,L</t>
+          <t>[新品上市🎁贈可拆卸肩帶]無肩帶內衣 平口內衣 抹胸 隱形內衣 胸罩 小胸內衣::高級灰,L｜推薦80A/80B</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -4982,7 +4982,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::冰川白,M</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::冰川白,L</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -4997,7 +4997,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶咖色,L</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::冰川白,M</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -5012,7 +5012,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶咖色,M</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶咖色,L</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -5027,7 +5027,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶咖色,XL</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶咖色,M</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5042,7 +5042,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶油黃,L</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶咖色,XL</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶油黃,M</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶油黃,L</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5072,7 +5072,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶油黃,XL</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶油黃,M</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5087,7 +5087,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::薄荷綠,L</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::奶油黃,XL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5102,7 +5102,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::薄荷綠,M</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::薄荷綠,L</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5117,7 +5117,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::薄荷綠,XL</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::薄荷綠,M</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5132,7 +5132,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::輕氧藍,L</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::薄荷綠,XL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5147,7 +5147,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::輕氧藍,M</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::輕氧藍,L</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5162,7 +5162,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::輕氧藍,XL</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::輕氧藍,M</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5177,7 +5177,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::雅黑色,L</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::輕氧藍,XL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5192,7 +5192,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::雅黑色,M</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::雅黑色,L</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5207,7 +5207,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::雅黑色,XL</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::雅黑色,M</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5222,7 +5222,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::楓木色,F</t>
+          <t>[新品上市🧊超薄速乾面膜褲]涼感內褲 女內褲 冰絲內褲 無痕內褲::雅黑色,XL</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5237,7 +5237,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::綠蘿紗,F</t>
+          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::楓木色,F</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5252,7 +5252,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::綠蘿紗,XL</t>
+          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::綠蘿紗,F</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5267,7 +5267,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::羊毛色,F</t>
+          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::綠蘿紗,XL</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5282,7 +5282,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::羊毛色,XL</t>
+          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::羊毛色,F</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5297,7 +5297,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::肉桂粉,F</t>
+          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::羊毛色,XL</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5312,7 +5312,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::肉桂粉,XL</t>
+          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::肉桂粉,F</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5327,7 +5327,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::黑色,F</t>
+          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::肉桂粉,XL</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5342,7 +5342,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】深藍色,L ➜建議70-75KG</t>
+          <t>[新品上市🩹秒變小蠻腰]高腰內褲 女內褲 收腹褲 塑身褲 提臀褲::黑色,F</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】深藍色,M ➜建議60-65KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】深藍色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5372,7 +5372,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】深藍色,S ➜建議50-55KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】深藍色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5387,7 +5387,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】深藍色,XL ➜建議80-85KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】深藍色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5395,26 +5395,14 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>HME03002-SO-DN-XL</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>HME03002</t>
-        </is>
-      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺灰色,L ➜建議70-75KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】深藍色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -5422,14 +5410,26 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>HME03002-SO-DN-XL</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺灰色,M ➜建議60-65KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺灰色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -5444,7 +5444,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺灰色,S ➜建議50-55KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺灰色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -5459,7 +5459,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺灰色,XL ➜建議80-85KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺灰色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -5474,7 +5474,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺綠色,L ➜建議70-75KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺灰色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -5489,7 +5489,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺綠色,M ➜建議60-65KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺綠色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -5504,7 +5504,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺綠色,S ➜建議50-55KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺綠色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺綠色,XL ➜建議80-85KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺綠色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】黑灰色,L ➜建議70-75KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】淺綠色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -5549,7 +5549,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】黑灰色,M ➜建議60-65KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】黑灰色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -5564,7 +5564,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】黑灰色,S ➜建議50-55KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】黑灰色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -5579,7 +5579,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】黑灰色,XL ➜建議80-85KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】黑灰色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -5587,26 +5587,14 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>HME03002-SO-BK-XL</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>HME03002</t>
-        </is>
-      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗深藍色,L ➜建議70-75KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】黑灰色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -5614,14 +5602,26 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr"/>
-      <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr"/>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗深藍色,M ➜建議60-65KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗深藍色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗深藍色,S ➜建議50-55KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗深藍色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -5651,7 +5651,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗深藍色,XL ➜建議80-85KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗深藍色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -5659,26 +5659,14 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>HME03002-ST-DN-XL</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>HME03002</t>
-        </is>
-      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺灰色,L ➜建議70-75KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗深藍色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -5686,14 +5674,26 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr"/>
-      <c r="D346" t="inlineStr"/>
-      <c r="E346" t="inlineStr"/>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>HME03002-ST-DN-XL</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺灰色,M ➜建議60-65KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺灰色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺灰色,S ➜建議50-55KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺灰色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -5723,7 +5723,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺灰色,XL ➜建議80-85KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺灰色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -5738,7 +5738,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺藍色,L ➜建議70-75KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺灰色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺藍色,M ➜建議60-65KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺藍色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -5768,7 +5768,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺藍色,S ➜建議50-55KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺藍色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -5783,7 +5783,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺藍色,XL ➜建議80-85KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺藍色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -5798,7 +5798,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗黑灰色,L ➜建議70-75KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗淺藍色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -5813,7 +5813,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗黑灰色,M ➜建議60-65KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗黑灰色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -5828,7 +5828,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗黑灰色,S ➜建議50-55KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗黑灰色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗黑灰色,XL ➜建議80-85KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗黑灰色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -5858,7 +5858,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::2倍厚,A罩杯</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗黑灰色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::2倍厚,B罩杯</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::2倍厚,A罩杯</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -5888,7 +5888,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::2倍厚,C罩杯</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::2倍厚,B罩杯</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -5903,7 +5903,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::2倍厚,D罩杯</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::2倍厚,C罩杯</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -5918,7 +5918,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::4倍厚,A罩杯</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::2倍厚,D罩杯</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -5933,7 +5933,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::4倍厚,B罩杯</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::4倍厚,A罩杯</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -5948,7 +5948,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::4倍厚,C罩杯</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::4倍厚,B罩杯</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -5963,7 +5963,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::4倍厚,D罩杯</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::4倍厚,C罩杯</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::立體杯,A罩杯</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::4倍厚,D罩杯</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -5993,7 +5993,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::立體杯,B罩杯</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::立體杯,A罩杯</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -6008,7 +6008,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::立體杯,C罩杯</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::立體杯,B罩杯</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -6023,7 +6023,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::立體杯,D罩杯</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::立體杯,C罩杯</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -6038,7 +6038,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>[獨特短頸衣架🧺衣櫃空間省更多]無痕衣架 衣架 防滑衣架 晾衣架 吊衣架::奶霧灰｜單支入</t>
+          <t>[水感超防掉💧升杯小祕密]隱形內衣 胸貼 nubar 無肩帶內衣 小胸內衣::立體杯,D罩杯</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -6053,7 +6053,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>[獨特短頸衣架🧺衣櫃空間省更多]無痕衣架 衣架 防滑衣架 晾衣架 吊衣架::燕麥白｜單支入</t>
+          <t>[獨特短頸衣架🧺衣櫃空間省更多]無痕衣架 衣架 防滑衣架 晾衣架 吊衣架::奶霧灰｜單支入</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -6068,7 +6068,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>[現貨📦便攜保護掛袋]眼鏡袋 眼鏡盒 眼鏡收納包 眼鏡收納盒 太陽眼鏡盒 貓咪造型::棕色小熊</t>
+          <t>[獨特短頸衣架🧺衣櫃空間省更多]無痕衣架 衣架 防滑衣架 晾衣架 吊衣架::燕麥白｜單支入</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6083,7 +6083,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>[現貨📦便攜保護掛袋]眼鏡袋 眼鏡盒 眼鏡收納包 眼鏡收納盒 太陽眼鏡盒 貓咪造型::灰白小貓</t>
+          <t>[現貨📦便攜保護掛袋]眼鏡袋 眼鏡盒 眼鏡收納包 眼鏡收納盒 太陽眼鏡盒 貓咪造型::棕色小熊</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6098,7 +6098,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>[現貨📦便攜保護掛袋]眼鏡袋 眼鏡盒 眼鏡收納包 眼鏡收納盒 太陽眼鏡盒 貓咪造型::黃白小貓</t>
+          <t>[現貨📦便攜保護掛袋]眼鏡袋 眼鏡盒 眼鏡收納包 眼鏡收納盒 太陽眼鏡盒 貓咪造型::灰白小貓</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6113,7 +6113,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>[現貨📦四小時保溫]保溫便當袋 便當袋 便當袋日本 餐袋 小提袋 午餐袋::可可棕,約22.5x14*24cm</t>
+          <t>[現貨📦便攜保護掛袋]眼鏡袋 眼鏡盒 眼鏡收納包 眼鏡收納盒 太陽眼鏡盒 貓咪造型::黃白小貓</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6128,7 +6128,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>[現貨📦四小時保溫]保溫便當袋 便當袋 便當袋日本 餐袋 小提袋 午餐袋::大象灰,約22.5x14*24cm</t>
+          <t>[現貨📦四小時保溫]保溫便當袋 便當袋 便當袋日本 餐袋 小提袋 午餐袋::可可棕,約22.5x14*24cm</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6143,7 +6143,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>[現貨📦旅行必備的質感化妝收納包]收納包 化妝包 旅行包 盥洗包 小化妝包::【L號】灰藕粉</t>
+          <t>[現貨📦四小時保溫]保溫便當袋 便當袋 便當袋日本 餐袋 小提袋 午餐袋::大象灰,約22.5x14*24cm</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6158,7 +6158,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>[現貨📦磁吸立式好拿取刷具包]刷具收納 化妝包 化妝品收納 刷具包::白蛋色｜約20x9x5cm</t>
+          <t>[現貨📦旅行必備的質感化妝收納包]收納包 化妝包 旅行包 盥洗包 小化妝包::【L號】灰藕粉</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6173,7 +6173,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>[現貨📦磁吸立式好拿取刷具包]刷具收納 化妝包 化妝品收納 刷具包::霧玫瑰｜約20x9x5cm</t>
+          <t>[現貨📦磁吸立式好拿取刷具包]刷具收納 化妝包 化妝品收納 刷具包::白蛋色｜約20x9x5cm</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6188,7 +6188,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>[現貨📦立式好拿取刷具包]刷具收納 化妝包 化妝品收納 保養品收納 刷具包::卡其色,8×6×20cm</t>
+          <t>[現貨📦磁吸立式好拿取刷具包]刷具收納 化妝包 化妝品收納 刷具包::霧玫瑰｜約20x9x5cm</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6203,7 +6203,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>[現貨📦衣物分裝好幫手]旅行壓縮袋 旅行收納袋 行李收納袋 壓縮收納袋 衣物收納 衣服收納袋 髒衣袋::米色,單個入</t>
+          <t>[現貨📦立式好拿取刷具包]刷具收納 化妝包 化妝品收納 保養品收納 刷具包::卡其色,8×6×20cm</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6218,7 +6218,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>[現貨📦衣物分裝好幫手]旅行壓縮袋 旅行收納袋 行李收納袋 壓縮收納袋 衣物收納 衣服收納袋 髒衣袋::粉色,單個入</t>
+          <t>[現貨📦衣物分裝好幫手]旅行壓縮袋 旅行收納袋 行李收納袋 壓縮收納袋 衣物收納 衣服收納袋 髒衣袋::米色,單個入</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>[現貨📦衣物分裝好幫手]旅行壓縮袋 旅行收納袋 行李收納袋 壓縮收納袋 衣物收納 衣服收納袋 髒衣袋::藍色,單個入</t>
+          <t>[現貨📦衣物分裝好幫手]旅行壓縮袋 旅行收納袋 行李收納袋 壓縮收納袋 衣物收納 衣服收納袋 髒衣袋::粉色,單個入</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>[現貨📦衣物分裝好幫手]旅行壓縮袋 旅行收納袋 行李收納袋 壓縮收納袋 衣物收納 衣服收納袋 髒衣袋::黑色,單個入</t>
+          <t>[現貨📦衣物分裝好幫手]旅行壓縮袋 旅行收納袋 行李收納袋 壓縮收納袋 衣物收納 衣服收納袋 髒衣袋::藍色,單個入</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6263,7 +6263,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::燕麥米,L｜27x19cm</t>
+          <t>[現貨📦衣物分裝好幫手]旅行壓縮袋 旅行收納袋 行李收納袋 壓縮收納袋 衣物收納 衣服收納袋 髒衣袋::黑色,單個入</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6278,7 +6278,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::燕麥米,M｜19x13.5cm</t>
+          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::燕麥米,L｜27x19cm</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6293,7 +6293,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::燕麥米,S｜13.5x10cm</t>
+          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::燕麥米,M｜19x13.5cm</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6308,7 +6308,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::藍灰色,L｜27x19cm</t>
+          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::燕麥米,S｜13.5x10cm</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -6323,7 +6323,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::藍灰色,M｜19x13.5cm</t>
+          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::藍灰色,L｜27x19cm</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -6338,7 +6338,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::藍灰色,S｜13.5x10cm</t>
+          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::藍灰色,M｜19x13.5cm</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -6353,7 +6353,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>[現貨📦輕薄便攜可折疊]旅行衣架 曬衣夾 旅行衣架 折疊衣架 曬衣::碧波紋,【六夾】33x17.5cm</t>
+          <t>[現貨📦超萬用小物袋]網格收納袋 文件袋 透明收納袋 紗網袋 印章袋 文具袋 網格筆袋 大中小 防水::藍灰色,S｜13.5x10cm</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -6368,7 +6368,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>[現貨📦附可拆卸髒衣袋]內衣褲收納 旅行收納包 旅行收納袋 內衣收納 襪子收納 髒衣袋::可可棕</t>
+          <t>[現貨📦輕薄便攜可折疊]旅行衣架 曬衣夾 旅行衣架 折疊衣架 曬衣::碧波紋,【六夾】33x17.5cm</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>[白T不透色✨粉底隱形內衣]粉底液內衣 胸罩 無痕內衣 隱形內衣 無鋼圈內衣 內衣::【寬肩帶】深膚色,F均碼</t>
+          <t>[現貨📦附可拆卸髒衣袋]內衣褲收納 旅行收納包 旅行收納袋 內衣收納 襪子收納 髒衣袋::可可棕</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -6398,7 +6398,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>[白T不透色✨粉底隱形內衣]粉底液內衣 胸罩 無痕內衣 隱形內衣 無鋼圈內衣 內衣::【寬肩帶】深膚色,XXL加大碼</t>
+          <t>[白T不透色✨粉底隱形內衣]粉底液內衣 胸罩 無痕內衣 隱形內衣 無鋼圈內衣 內衣::【寬肩帶】深膚色,F均碼</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -6413,7 +6413,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>[白T不透色✨粉底隱形內衣]粉底液內衣 胸罩 無痕內衣 隱形內衣 無鋼圈內衣 內衣::【細肩帶】抹茶綠,XXL加大碼</t>
+          <t>[白T不透色✨粉底隱形內衣]粉底液內衣 胸罩 無痕內衣 隱形內衣 無鋼圈內衣 內衣::【寬肩帶】深膚色,XXL加大碼</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6428,7 +6428,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>[白T不透色✨粉底隱形內衣]粉底液內衣 胸罩 無痕內衣 隱形內衣 無鋼圈內衣 內衣::【細肩帶】淺膚色,XXL加大碼</t>
+          <t>[白T不透色✨粉底隱形內衣]粉底液內衣 胸罩 無痕內衣 隱形內衣 無鋼圈內衣 內衣::【細肩帶】抹茶綠,XXL加大碼</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -6443,7 +6443,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>[秋冬必備的溫柔韓系]長版針織外套 針織外套 中長版外套 長版外套 女外套 毛衣外套 冬季外套::摩卡棕</t>
+          <t>[白T不透色✨粉底隱形內衣]粉底液內衣 胸罩 無痕內衣 隱形內衣 無鋼圈內衣 內衣::【細肩帶】淺膚色,XXL加大碼</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -6458,7 +6458,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜圓領,L</t>
+          <t>[秋冬必備的溫柔韓系]長版針織外套 針織外套 中長版外套 長版外套 女外套 毛衣外套 冬季外套::摩卡棕</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -6473,7 +6473,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜圓領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜圓領,L</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -6488,7 +6488,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜圓領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜圓領,M</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -6503,7 +6503,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜立領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜圓領,XL</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜高領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜立領,M</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -6533,7 +6533,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜高領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜高領,M</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -6548,7 +6548,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜圓領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::淺卡其｜高領,XL</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -6563,7 +6563,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜圓領,S</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜圓領,L</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -6578,7 +6578,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜圓領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜圓領,S</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -6593,7 +6593,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜立領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜圓領,XL</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -6608,7 +6608,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜立領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜立領,L</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -6623,7 +6623,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜立領,S</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜立領,M</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -6638,7 +6638,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜高領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜立領,S</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜高領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜高領,L</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -6668,7 +6668,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜圓領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::灰色｜高領,M</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -6683,7 +6683,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜圓領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜圓領,L</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -6698,7 +6698,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜圓領,S</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜圓領,M</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -6713,7 +6713,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜圓領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜圓領,S</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -6728,7 +6728,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜立領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜圓領,XL</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -6743,7 +6743,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜立領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜立領,L</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -6758,7 +6758,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜立領,S</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜立領,M</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -6773,7 +6773,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜立領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜立領,S</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -6788,7 +6788,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜高領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜立領,XL</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -6803,7 +6803,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜高領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜高領,L</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -6818,7 +6818,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜高領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜高領,M</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -6833,7 +6833,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜圓領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::白色｜高領,XL</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -6848,7 +6848,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜圓領,S</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜圓領,L</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -6863,7 +6863,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜圓領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜圓領,S</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -6878,7 +6878,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜立領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜圓領,XL</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜高領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜立領,XL</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -6908,7 +6908,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜高領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜高領,M</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -6923,7 +6923,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜圓領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::粉色｜高領,XL</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -6938,7 +6938,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜圓領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜圓領,L</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -6953,7 +6953,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜立領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜圓領,XL</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -6968,7 +6968,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜立領,S</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜立領,L</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -6983,7 +6983,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜立領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜立領,S</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -6998,7 +6998,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜高領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜立領,XL</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -7013,7 +7013,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜高領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜高領,M</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -7028,7 +7028,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜圓領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::霧藍色｜高領,XL</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -7043,7 +7043,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜圓領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜圓領,L</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -7058,7 +7058,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜圓領,S</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜圓領,M</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -7073,7 +7073,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜圓領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜圓領,S</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜立領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜圓領,XL</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7103,7 +7103,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜立領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜立領,L</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7118,7 +7118,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜立領,S</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜立領,M</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7133,7 +7133,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜立領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜立領,S</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7141,26 +7141,14 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色XL]</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>HFA02001-MN-BK-XL</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>HFA02001</t>
-        </is>
-      </c>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜高領,L</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜立領,XL</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7168,14 +7156,26 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr"/>
-      <c r="D444" t="inlineStr"/>
-      <c r="E444" t="inlineStr"/>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【立領】黑色XL]</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>HFA02001-MN-BK-XL</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜高領,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜高領,L</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7183,26 +7183,14 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色M]</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>HFA02001-TN-BK-M</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>HFA02001</t>
-        </is>
-      </c>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜高領,S</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜高領,M</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7210,14 +7198,26 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
-      <c r="E446" t="inlineStr"/>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【高領】黑色M]</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-BK-M</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜高領,XL</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜高領,S</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -7232,7 +7232,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::咖啡色,M</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜高領,XL</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -7247,7 +7247,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::灰色,M</t>
+          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::咖啡色,M</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -7262,7 +7262,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::灰色,XL</t>
+          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::灰色,M</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -7277,7 +7277,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::白色,M</t>
+          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::灰色,XL</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::白色,XL</t>
+          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::白色,M</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -7307,7 +7307,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::薄荷綠,M</t>
+          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::白色,XL</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -7322,7 +7322,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::黑色,L</t>
+          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::薄荷綠,M</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -7337,7 +7337,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::黑色,M</t>
+          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::黑色,L</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -7352,7 +7352,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::黑色,XL</t>
+          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::黑色,M</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -7367,7 +7367,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::淺卡其｜圓領,L</t>
+          <t>[秋冬打底神隊友🍁舒適羅紋]長袖內搭 薄長袖 內搭長袖 內搭衣 打底衣 針織長袖::黑色,XL</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::灰色｜高領,XL</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::淺卡其｜圓領,L</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -7397,7 +7397,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜圓領,XL</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::灰色｜高領,XL</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -7412,7 +7412,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜立領,L</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜圓領,XL</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -7427,7 +7427,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜立領,S</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜立領,L</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -7442,7 +7442,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜立領,XL</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜立領,S</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -7457,7 +7457,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜高領,L</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜立領,XL</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -7472,7 +7472,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜高領,XL</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜高領,L</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -7487,7 +7487,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::粉色｜圓領,L</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::白色｜高領,XL</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -7502,7 +7502,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::霧藍色｜圓領,XL</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::粉色｜圓領,L</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -7517,7 +7517,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::霧藍色｜立領,XL</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::霧藍色｜圓領,XL</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -7532,7 +7532,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::霧藍色｜高領,M</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::霧藍色｜立領,XL</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -7547,7 +7547,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜圓領,M</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::霧藍色｜高領,M</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -7562,7 +7562,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜圓領,XL</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜圓領,M</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -7577,7 +7577,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜立領,L</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜圓領,XL</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜立領,M</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜立領,L</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -7607,7 +7607,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜立領,XL</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜立領,M</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -7622,7 +7622,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜高領,L</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜立領,XL</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -7637,7 +7637,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜高領,M</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜高領,L</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -7652,7 +7652,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜高領,XL</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜高領,M</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -7667,7 +7667,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::沙粉色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
+          <t>[秋冬莫代爾打底衣🍁三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 打底衫 高領上衣 高領內搭 半高領::黑色｜高領,XL</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -7682,7 +7682,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::沙粉色,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::沙粉色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::沙粉色,S ➜建議𝟰𝟬-𝟱𝟬𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::沙粉色,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -7712,7 +7712,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::沙粉色,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::沙粉色,S ➜建議𝟰𝟬-𝟱𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -7727,7 +7727,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深岩灰,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::沙粉色,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -7742,7 +7742,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深岩灰,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深岩灰,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -7757,7 +7757,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深岩灰,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深岩灰,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -7772,7 +7772,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深海藍,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深岩灰,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -7787,7 +7787,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深海藍,S ➜建議𝟰𝟬-𝟱𝟬𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深海藍,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -7802,7 +7802,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深海藍,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深海藍,S ➜建議𝟰𝟬-𝟱𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -7817,7 +7817,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::白色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::深海藍,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -7832,7 +7832,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::白色,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::白色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -7847,7 +7847,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::白色,S ➜建議𝟰𝟬-𝟱𝟬𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::白色,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -7862,7 +7862,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::麻灰色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::白色,S ➜建議𝟰𝟬-𝟱𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -7877,7 +7877,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::麻灰色,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::麻灰色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -7892,7 +7892,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::麻灰色,S ➜建議𝟰𝟬-𝟱𝟬𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::麻灰色,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -7907,7 +7907,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::麻灰色,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::麻灰色,S ➜建議𝟰𝟬-𝟱𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -7922,7 +7922,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::黑色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::麻灰色,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::黑色,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::黑色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -7952,7 +7952,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::黑色,S ➜建議𝟰𝟬-𝟱𝟬𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::黑色,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -7967,7 +7967,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::黑色,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::黑色,S ➜建議𝟰𝟬-𝟱𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -7982,7 +7982,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::140克微中絨｜參考穿著溫度15-20℃,膚色</t>
+          <t>[穿搭必備✨經典男女大學TEE]長袖t恤 大學t 長袖上衣 情侶裝 情侶衣::黑色,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -7997,7 +7997,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::140克微中絨｜參考穿著溫度15-20℃,黑色</t>
+          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::140克微中絨｜參考穿著溫度15-20℃,膚色</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -8012,7 +8012,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::180克中厚絨｜參考穿著溫度10-15℃,膚色</t>
+          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::140克微中絨｜參考穿著溫度15-20℃,黑色</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -8027,7 +8027,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::180克中厚絨｜參考穿著溫度10-15℃,黑色</t>
+          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::180克中厚絨｜參考穿著溫度10-15℃,膚色</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -8042,7 +8042,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::280克超厚絨｜參考穿著溫度5-10℃,膚色</t>
+          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::180克中厚絨｜參考穿著溫度10-15℃,黑色</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -8057,7 +8057,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::280克超厚絨｜參考穿著溫度5-10℃,黑色</t>
+          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::280克超厚絨｜參考穿著溫度5-10℃,膚色</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -8072,7 +8072,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::380克極厚絨｜參考穿著溫度0-5℃,膚色</t>
+          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::280克超厚絨｜參考穿著溫度5-10℃,黑色</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -8087,7 +8087,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::380克極厚絨｜參考穿著溫度0-5℃,黑色</t>
+          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::380克極厚絨｜參考穿著溫度0-5℃,膚色</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8102,7 +8102,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::140克微中絨｜參考穿著溫度15-20℃,膚色</t>
+          <t>[粉底級遮瑕．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::380克極厚絨｜參考穿著溫度0-5℃,黑色</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -8110,26 +8110,14 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>裸感厚絨光腿褲襪[膚色140G]</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>HFF02001-SK-140G</t>
-        </is>
-      </c>
-      <c r="E506" t="inlineStr">
-        <is>
-          <t>HFF02001</t>
-        </is>
-      </c>
+      <c r="C506" t="inlineStr"/>
+      <c r="D506" t="inlineStr"/>
+      <c r="E506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::140克微中絨｜參考穿著溫度15-20℃,黑色</t>
+          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::140克微中絨｜參考穿著溫度15-20℃,膚色</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -8137,14 +8125,26 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr"/>
-      <c r="E507" t="inlineStr"/>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>裸感厚絨光腿褲襪[膚色140G]</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-140G</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>HFF02001</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::180克中厚絨｜參考穿著溫度10-15℃,膚色</t>
+          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::140克微中絨｜參考穿著溫度15-20℃,黑色</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -8159,7 +8159,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::180克中厚絨｜參考穿著溫度10-15℃,黑色</t>
+          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::180克中厚絨｜參考穿著溫度10-15℃,膚色</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -8174,7 +8174,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::280克超厚絨｜參考穿著溫度5-10℃,膚色</t>
+          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::180克中厚絨｜參考穿著溫度10-15℃,黑色</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::280克超厚絨｜參考穿著溫度5-10℃,黑色</t>
+          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::280克超厚絨｜參考穿著溫度5-10℃,膚色</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -8204,7 +8204,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::380克極厚絨｜參考穿著溫度0-5℃,膚色</t>
+          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::280克超厚絨｜參考穿著溫度5-10℃,黑色</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -8219,7 +8219,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::380克極厚絨｜參考穿著溫度0-5℃,黑色</t>
+          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::380克極厚絨｜參考穿著溫度0-5℃,膚色</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -8234,7 +8234,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::冰川藍,L ➜建議70-75KG</t>
+          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::380克極厚絨｜參考穿著溫度0-5℃,黑色</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -8249,7 +8249,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::冰川藍,M ➜建議60-65KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::冰川藍,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -8264,7 +8264,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::冰川藍,S ➜建議50-55KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::冰川藍,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -8279,7 +8279,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::冰川藍,XL ➜建議80-85KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::冰川藍,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -8294,7 +8294,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::夜空藍,L ➜建議70-75KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::冰川藍,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -8309,7 +8309,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::夜空藍,M ➜建議60-65KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::夜空藍,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::夜空藍,S ➜建議50-55KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::夜空藍,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -8339,7 +8339,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::夜空藍,XL ➜建議80-85KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::夜空藍,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -8354,7 +8354,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::星耀黑,L ➜建議70-75KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::夜空藍,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -8369,7 +8369,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::星耀黑,M ➜建議60-65KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::星耀黑,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -8384,7 +8384,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::星耀黑,S ➜建議50-55KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::星耀黑,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -8399,7 +8399,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::星耀黑,XL ➜建議80-85KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::星耀黑,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -8414,7 +8414,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::淺花灰,L ➜建議70-75KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::星耀黑,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -8429,7 +8429,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::淺花灰,M ➜建議60-65KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::淺花灰,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -8444,7 +8444,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::淺花灰,S ➜建議50-55KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::淺花灰,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -8459,7 +8459,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::淺花灰,XL ➜建議80-85KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::淺花灰,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::炭灰色,L ➜建議70-75KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::淺花灰,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -8489,7 +8489,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::炭灰色,M ➜建議60-65KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::炭灰色,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -8504,7 +8504,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::炭灰色,S ➜建議50-55KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::炭灰色,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -8519,7 +8519,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::炭灰色,XL ➜建議80-85KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::炭灰色,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -8534,7 +8534,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::草木綠,L ➜建議70-75KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::炭灰色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -8549,7 +8549,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::草木綠,M ➜建議60-65KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::草木綠,L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -8564,7 +8564,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::草木綠,S ➜建議50-55KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::草木綠,M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -8579,7 +8579,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::草木綠,XL ➜建議80-85KG</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::草木綠,S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -8594,7 +8594,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>[網美辣妹風🔥免穿內衣] 吊帶背心 針織背心 短版背心 固定胸墊 內搭外穿 小可愛::可可色,F</t>
+          <t>[純棉寬鬆☁居家無拘束]四角褲 男生內褲 男士內褲 男內褲 純棉內褲 四角平口褲 男性內褲 內褲男::草木綠,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -8609,7 +8609,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>[網美辣妹風🔥免穿內衣] 吊帶背心 針織背心 短版背心 固定胸墊 內搭外穿 小可愛::深灰色,F</t>
+          <t>[網美辣妹風🔥免穿內衣] 吊帶背心 針織背心 短版背心 固定胸墊 內搭外穿 小可愛::可可色,F</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -8624,7 +8624,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::可可棕</t>
+          <t>[網美辣妹風🔥免穿內衣] 吊帶背心 針織背心 短版背心 固定胸墊 內搭外穿 小可愛::深灰色,F</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -8639,7 +8639,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::奶白色</t>
+          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::可可棕</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -8654,7 +8654,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::嬰兒藍</t>
+          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::奶白色</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -8669,7 +8669,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::櫻花粉</t>
+          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::嬰兒藍</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -8684,7 +8684,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::雲朵灰</t>
+          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::櫻花粉</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -8699,7 +8699,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::黑色</t>
+          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::雲朵灰</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -8714,7 +8714,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【四季薄款】基本款-復古藍,XL</t>
+          <t>[舒適不勒頭🎀贈送洗臉腕帶]洗臉髮帶 頭帶 洗臉髮箍 運動髮帶 運動頭巾::黑色</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -8729,7 +8729,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【四季薄款】嬌小款-復古藍,L</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【四季薄款】基本款-復古藍,XL</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -8744,7 +8744,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】基本款-復古藍,L</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【四季薄款】嬌小款-復古藍,L</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -8759,7 +8759,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】基本款-復古藍,M</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】基本款-復古藍,L</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -8774,7 +8774,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】基本款-復古藍,XL</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】基本款-復古藍,M</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -8789,7 +8789,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】基本款-黑色,L</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】基本款-復古藍,XL</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -8804,7 +8804,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-復古藍,L</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】基本款-黑色,L</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -8819,7 +8819,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-復古藍,M</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-復古藍,L</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -8834,7 +8834,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-復古藍,XL</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-復古藍,M</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -8849,7 +8849,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-白色,M</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-復古藍,XL</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -8864,7 +8864,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-黑色,L</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-白色,M</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -8879,7 +8879,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-黑色,XL</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-黑色,L</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -8894,7 +8894,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>[裙褲好收納的秘密武器]褲架 衣架 褲夾 晾衣架 吊衣架 防滑衣架::淺灰色</t>
+          <t>[舒適鬆緊腰．小個子也可穿]牛仔寬褲 刷毛牛仔褲 闊腿褲 寬褲 美式寬褲 加絨牛仔褲 小個子 鬆緊 秋冬 保暖 加絨 女::【秋冬刷毛款】嬌小款-黑色,XL</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -8909,7 +8909,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>[補妝小物一包搞定]小化妝包 收納包 隨身小包 化妝包 隨身包::【M號】燕麥色</t>
+          <t>[裙褲好收納的秘密武器]褲架 衣架 褲夾 晾衣架 吊衣架 防滑衣架::淺灰色</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -8924,7 +8924,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>[補妝小物一包搞定]小化妝包 收納包 隨身小包 化妝包 隨身包::【S號】燕麥色</t>
+          <t>[補妝小物一包搞定]小化妝包 收納包 隨身小包 化妝包 隨身包::【M號】燕麥色</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -8939,7 +8939,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>[補妝小物一包搞定]小化妝包 收納包 隨身小包 化妝包 隨身包::【S號】藍灰色</t>
+          <t>[補妝小物一包搞定]小化妝包 收納包 隨身小包 化妝包 隨身包::【S號】燕麥色</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -8954,7 +8954,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::深湖藍,S</t>
+          <t>[補妝小物一包搞定]小化妝包 收納包 隨身小包 化妝包 隨身包::【S號】藍灰色</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::深湖藍,XL</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::深湖藍,S</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -8984,7 +8984,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::白色,L</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::深湖藍,XL</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -8999,7 +8999,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::白色,M</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::白色,L</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -9014,7 +9014,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::白色,S</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::白色,M</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -9029,7 +9029,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::白色,XL</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::白色,S</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -9044,7 +9044,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::磚紅色,XL</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::白色,XL</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -9059,7 +9059,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::花灰色,L</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::磚紅色,XL</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -9074,7 +9074,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::花灰色,M</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::花灰色,L</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -9089,7 +9089,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::花灰色,XL</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::花灰色,M</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -9104,7 +9104,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::黑色,L</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::花灰色,XL</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -9119,7 +9119,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::黑色,M</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::黑色,L</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -9134,7 +9134,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::黑色,S</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::黑色,M</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -9149,7 +9149,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::黑色,XL</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::黑色,S</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -9164,7 +9164,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::淺卡其｜立領,S</t>
+          <t>[襯衫西裝族首選💼超輕薄內著]男背心 男內著 吊嘎 背心男 內搭背心::黑色,XL</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -9179,7 +9179,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::淺卡其｜立領,XL</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::淺卡其｜立領,S</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -9194,7 +9194,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::灰色｜立領,M</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::淺卡其｜立領,XL</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -9209,7 +9209,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::灰色｜高領,L</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::灰色｜立領,M</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -9224,7 +9224,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::灰色｜高領,M</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::灰色｜高領,L</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -9239,7 +9239,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::灰色｜高領,XL</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::灰色｜高領,M</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -9254,7 +9254,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::白色｜立領,M</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::灰色｜高領,XL</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -9269,7 +9269,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::白色｜立領,S</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::白色｜立領,M</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -9284,7 +9284,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::白色｜高領,M</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::白色｜立領,S</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -9299,7 +9299,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::粉色｜圓領,S</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::白色｜高領,M</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -9314,7 +9314,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::粉色｜立領,L</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::粉色｜圓領,S</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -9329,7 +9329,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::粉色｜立領,S</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::粉色｜立領,L</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -9344,7 +9344,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::霧藍色｜立領,M</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::粉色｜立領,S</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -9359,7 +9359,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜圓領,L</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::霧藍色｜立領,M</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -9374,7 +9374,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜圓領,XL</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜圓領,L</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -9389,7 +9389,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜立領,L</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜圓領,XL</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -9404,7 +9404,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜立領,M</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜立領,L</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -9419,7 +9419,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜立領,XL</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜立領,M</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -9434,7 +9434,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜高領,L</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜立領,XL</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -9449,7 +9449,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜高領,M</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜高領,L</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -9464,7 +9464,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜高領,XL</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜高領,M</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -9479,7 +9479,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>[超值三件組．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::140克薄絨｜建議溫度15-20℃,【三件組】膚色</t>
+          <t>[親膚莫代爾．三種領型]內搭長袖 打底衣 高領打底衣 打底衫 內搭上衣 圓領 高領 半高領 小立領 冬天 冬季 長袖 女::黑色｜高領,XL</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -9494,7 +9494,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>[超值三件組．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::140克薄絨｜建議溫度15-20℃,【三件組】黑色</t>
+          <t>[超值三件組．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::140克薄絨｜建議溫度15-20℃,【三件組】膚色</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -9509,7 +9509,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>[超值三件組．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::180克厚絨｜建議溫度10-15℃,【三件組】膚色</t>
+          <t>[超值三件組．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::140克薄絨｜建議溫度15-20℃,【三件組】黑色</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -9524,7 +9524,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>[超值三件組．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::280克加厚絨｜建議溫度5-10℃,【三件組】膚色</t>
+          <t>[超值三件組．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::180克厚絨｜建議溫度10-15℃,【三件組】膚色</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -9539,7 +9539,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>[超值三件組．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::380克特厚絨｜建議溫度0-5℃,【三件組】膚色</t>
+          <t>[超值三件組．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::280克加厚絨｜建議溫度5-10℃,【三件組】膚色</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -9554,7 +9554,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>[超值三件組💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::140克薄絨｜建議溫度15-20℃,【三件組】膚色</t>
+          <t>[超值三件組．寒流級超厚絨]刷毛褲襪 光腿神器 保暖褲襪 光腿絲襪 褲襪 光腿 冬天 黑色 膚色 保暖::380克特厚絨｜建議溫度0-5℃,【三件組】膚色</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -9569,7 +9569,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>[超值三件組💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::140克薄絨｜建議溫度15-20℃,【三件組】黑色</t>
+          <t>[超值三件組💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::140克薄絨｜建議溫度15-20℃,【三件組】膚色</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -9584,7 +9584,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>[超值三件組💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::180克厚絨｜建議溫度10-15℃,【三件組】膚色</t>
+          <t>[超值三件組💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::140克薄絨｜建議溫度15-20℃,【三件組】黑色</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -9599,7 +9599,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>[超值三件組💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::180克厚絨｜建議溫度10-15℃,【三件組】黑色</t>
+          <t>[超值三件組💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::180克厚絨｜建議溫度10-15℃,【三件組】膚色</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -9614,7 +9614,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>[超值三件組💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::380克特厚絨｜建議溫度0-5℃,【三件組】膚色</t>
+          <t>[超值三件組💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::180克厚絨｜建議溫度10-15℃,【三件組】黑色</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -9629,7 +9629,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>[超值大全配7件組．防變形☑️耐用細網] 內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵款【超值大全配7件組】</t>
+          <t>[超值三件組💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::380克特厚絨｜建議溫度0-5℃,【三件組】膚色</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -9644,7 +9644,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::亞麻棕,約185x75cm</t>
+          <t>[超值大全配7件組．防變形☑️耐用細網] 內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵款【超值大全配7件組】</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -9659,7 +9659,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::卡其色,約185x75cm</t>
+          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::亞麻棕,約185x75cm</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -9674,7 +9674,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::深灰色,約185x75cm</t>
+          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::卡其色,約185x75cm</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -9689,7 +9689,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::米白色,約185x75cm</t>
+          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::深灰色,約185x75cm</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -9704,7 +9704,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::酒紅色,約185x75cm</t>
+          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::米白色,約185x75cm</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -9719,7 +9719,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::黑色,約185x75cm</t>
+          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::酒紅色,約185x75cm</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -9734,7 +9734,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>[軟糯毛料好好穿☁️韓系寬鬆兩件組]毛衣套裝 秋冬套裝 慵懶風套裝 針織套裝 毛衣女 針織毛衣 針織短褲::花灰色,F</t>
+          <t>[超柔軟🤍秋冬外搭神器]針織披肩 披肩 披肩圍巾 三角披肩 外搭披肩::黑色,約185x75cm</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -9749,7 +9749,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::奶咖色,L</t>
+          <t>[軟糯毛料好好穿☁️韓系寬鬆兩件組]毛衣套裝 秋冬套裝 慵懶風套裝 針織套裝 毛衣女 針織毛衣 針織短褲::花灰色,F</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -9764,7 +9764,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::奶咖色,M</t>
+          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::奶咖色,L</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -9779,7 +9779,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::深灰色,M</t>
+          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::奶咖色,M</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -9794,7 +9794,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::燕麥白,L</t>
+          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::深灰色,M</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -9809,7 +9809,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::燕麥白,M</t>
+          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::燕麥白,L</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -9824,7 +9824,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::黑色,L</t>
+          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::燕麥白,M</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -9839,7 +9839,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::黑色,M</t>
+          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::黑色,L</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -9854,7 +9854,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>[軟萌系🤍冬天在家也要可可愛愛]睡衣裙 睡裙 長袖睡裙 冬天睡裙 珊瑚絨睡衣 絨毛睡衣::深灰色,L</t>
+          <t>[軟糯顯瘦✨秋冬遮肉必備]半身裙 長裙 A字裙 白色長裙 魚尾裙::黑色,M</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -9869,7 +9869,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>[軟萌系🤍冬天在家也要可可愛愛]睡衣裙 睡裙 長袖睡裙 冬天睡裙 珊瑚絨睡衣 絨毛睡衣::深灰色,XL</t>
+          <t>[軟萌系🤍冬天在家也要可可愛愛]睡衣裙 睡裙 長袖睡裙 冬天睡裙 珊瑚絨睡衣 絨毛睡衣::深灰色,L</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -9884,7 +9884,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>[軟萌系🤍冬天在家也要可可愛愛]睡衣裙 睡裙 長袖睡裙 冬天睡裙 珊瑚絨睡衣 絨毛睡衣::皮粉色,L</t>
+          <t>[軟萌系🤍冬天在家也要可可愛愛]睡衣裙 睡裙 長袖睡裙 冬天睡裙 珊瑚絨睡衣 絨毛睡衣::深灰色,XL</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -9899,7 +9899,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::燕麥色,L</t>
+          <t>[軟萌系🤍冬天在家也要可可愛愛]睡衣裙 睡裙 長袖睡裙 冬天睡裙 珊瑚絨睡衣 絨毛睡衣::皮粉色,L</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -9914,7 +9914,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::燕麥色,M</t>
+          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::燕麥色,L</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -9929,7 +9929,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::白杏色,L</t>
+          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::燕麥色,M</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -9944,7 +9944,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::白杏色,M</t>
+          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::白杏色,L</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -9959,7 +9959,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::黑色,L</t>
+          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::白杏色,M</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -9974,7 +9974,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::黑色,M</t>
+          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::黑色,L</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -9989,7 +9989,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::夜藍色,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+          <t>[遮肉大裙擺．柔軟糯米裙]針織長裙 針織裙 a字長裙 a字裙 高腰 傘裙 半身裙 白色 黑色 冬天 針織 女::黑色,M</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -10004,7 +10004,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::橄欖綠,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::夜藍色,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -10019,7 +10019,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::橄欖綠,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::橄欖綠,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -10034,7 +10034,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::煤灰色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::橄欖綠,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -10049,7 +10049,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::煤灰色,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::煤灰色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -10064,7 +10064,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::燕麥白,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::煤灰色,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -10079,7 +10079,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::燕麥白,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::燕麥白,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -10094,7 +10094,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::燕麥白,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::燕麥白,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -10109,7 +10109,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::石墨黑,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::燕麥白,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -10124,7 +10124,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::石墨黑,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::石墨黑,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -10139,7 +10139,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::石墨黑,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::石墨黑,M ➜建議𝟱𝟬-𝟲𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -10154,7 +10154,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::純白色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::石墨黑,XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -10169,7 +10169,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>[重磅純棉🔒內抽繩不外露]休閒短褲 男短褲 黑色短褲 五分褲 運動短褲男 男生短褲::卡其色,2XL</t>
+          <t>[重磅不透！寬鬆百搭] 厚磅短T 上衣 重磅短T 男生短袖 純棉T恤::純白色,L ➜建議𝟲𝟱-𝟴𝟬𝗞𝗚</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -10184,7 +10184,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>[重磅純棉🔒內抽繩不外露]休閒短褲 男短褲 黑色短褲 五分褲 運動短褲男 男生短褲::卡其色,L</t>
+          <t>[重磅純棉🔒內抽繩不外露]休閒短褲 男短褲 黑色短褲 五分褲 運動短褲男 男生短褲::卡其色,2XL</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -10199,7 +10199,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>[重磅純棉🔒內抽繩不外露]休閒短褲 男短褲 黑色短褲 五分褲 運動短褲男 男生短褲::卡其色,XL</t>
+          <t>[重磅純棉🔒內抽繩不外露]休閒短褲 男短褲 黑色短褲 五分褲 運動短褲男 男生短褲::卡其色,L</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -10214,7 +10214,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>[重磅純棉🔒內抽繩不外露]休閒短褲 男短褲 黑色短褲 五分褲 運動短褲男 男生短褲::咖啡色,XL</t>
+          <t>[重磅純棉🔒內抽繩不外露]休閒短褲 男短褲 黑色短褲 五分褲 運動短褲男 男生短褲::卡其色,XL</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>[重磅純棉🔒內抽繩不外露]休閒短褲 男短褲 黑色短褲 五分褲 運動短褲男 男生短褲::黑色,XL</t>
+          <t>[重磅純棉🔒內抽繩不外露]休閒短褲 男短褲 黑色短褲 五分褲 運動短褲男 男生短褲::咖啡色,XL</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -10244,7 +10244,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【中號】39*49cm</t>
+          <t>[重磅純棉🔒內抽繩不外露]休閒短褲 男短褲 黑色短褲 五分褲 運動短褲男 男生短褲::黑色,XL</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -10259,7 +10259,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【內衣用】17x17cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【中號】39*49cm</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -10274,7 +10274,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【加大】60x60cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【內衣用】17x17cm</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -10289,7 +10289,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【圓柱】23x34cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【加大】60x60cm</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -10304,7 +10304,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【大號】49x58cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【圓柱】23x34cm</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -10319,7 +10319,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【小號】25x32cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【大號】49x58cm</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -10334,7 +10334,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【迷你】25x29cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【小號】25x32cm</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -10349,7 +10349,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵款,【中號】39*49cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵,【迷你】25x29cm</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -10364,7 +10364,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【中號】39*49cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::花朵款,【中號】39*49cm</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -10379,7 +10379,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【內衣用】17x17cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【中號】39*49cm</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -10394,7 +10394,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【加大】60x60cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【內衣用】17x17cm</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -10409,7 +10409,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【圓柱】23x34cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【加大】60x60cm</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -10424,7 +10424,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【大號】49x58cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【圓柱】23x34cm</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -10439,7 +10439,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【小號】25x32cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【大號】49x58cm</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -10454,7 +10454,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【迷你】25x29cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【小號】25x32cm</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -10469,7 +10469,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏款,【中號】39*49cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏,【迷你】25x29cm</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -10484,7 +10484,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏款,【內衣用】17x17cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏款,【中號】39*49cm</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -10499,7 +10499,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏款,【大號】49x58cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏款,【內衣用】17x17cm</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -10514,7 +10514,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏款,【小號】25x32cm</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏款,【大號】49x58cm</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -10529,7 +10529,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>[限量下殺NG款🔥粉底級遮瑕✨寒流級超厚絨]光腿神器 保暖褲襪 褲襪 黑色膚色::微瑕𝗡𝗚品🆖140克微中絨,膚色</t>
+          <t>[防變形☑️耐用細網洗衣袋]內衣洗衣袋 洗衣袋 洗衣網 髒衣袋::銀杏款,【小號】25x32cm</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -10544,7 +10544,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>[限量下殺NG款🔥粉底級遮瑕✨寒流級超厚絨]光腿神器 保暖褲襪 褲襪 黑色膚色::微瑕𝗡𝗚品🆖180克中厚絨,膚色</t>
+          <t>[限量下殺NG款🔥粉底級遮瑕✨寒流級超厚絨]光腿神器 保暖褲襪 褲襪 黑色膚色::微瑕𝗡𝗚品🆖140克微中絨,膚色</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -10559,7 +10559,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>[限量下殺NG款🔥粉底級遮瑕✨寒流級超厚絨]光腿神器 保暖褲襪 褲襪 黑色膚色::微瑕𝗡𝗚品🆖280克超厚絨,膚色</t>
+          <t>[限量下殺NG款🔥粉底級遮瑕✨寒流級超厚絨]光腿神器 保暖褲襪 褲襪 黑色膚色::微瑕𝗡𝗚品🆖180克中厚絨,膚色</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -10574,7 +10574,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】灰色｜上衣+長褲套裝,L</t>
+          <t>[限量下殺NG款🔥粉底級遮瑕✨寒流級超厚絨]光腿神器 保暖褲襪 褲襪 黑色膚色::微瑕𝗡𝗚品🆖280克超厚絨,膚色</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -10589,7 +10589,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】灰色｜上衣+長褲套裝,M</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】灰色｜上衣+長褲套裝,L</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -10597,26 +10597,14 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
-        <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[灰色M]</t>
-        </is>
-      </c>
-      <c r="D671" t="inlineStr">
-        <is>
-          <t>HFH02001-GY-M</t>
-        </is>
-      </c>
-      <c r="E671" t="inlineStr">
-        <is>
-          <t>HFH02001</t>
-        </is>
-      </c>
+      <c r="C671" t="inlineStr"/>
+      <c r="D671" t="inlineStr"/>
+      <c r="E671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】灰色｜上衣+長褲套裝,XL</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】灰色｜上衣+長褲套裝,M</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -10624,14 +10612,26 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr"/>
-      <c r="E672" t="inlineStr"/>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[灰色M]</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>HFH02001-GY-M</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>HFH02001</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】珊瑚粉｜上衣+長褲套裝,L</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】灰色｜上衣+長褲套裝,XL</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -10646,7 +10646,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】珊瑚粉｜上衣+長褲套裝,M</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】珊瑚粉｜上衣+長褲套裝,L</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -10661,7 +10661,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】珊瑚粉｜上衣+長褲套裝,XL</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】珊瑚粉｜上衣+長褲套裝,M</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -10676,7 +10676,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】白色｜上衣+長褲套裝,L</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】珊瑚粉｜上衣+長褲套裝,XL</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -10691,7 +10691,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】白色｜上衣+長褲套裝,M</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】白色｜上衣+長褲套裝,L</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -10706,7 +10706,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】白色｜上衣+長褲套裝,XL</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】白色｜上衣+長褲套裝,M</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -10721,7 +10721,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】豆沙紅｜上衣+長褲套裝,L</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】白色｜上衣+長褲套裝,XL</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -10736,7 +10736,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】豆沙紅｜上衣+長褲套裝,M</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】豆沙紅｜上衣+長褲套裝,L</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -10751,7 +10751,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】豆沙紅｜上衣+長褲套裝,XL</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】豆沙紅｜上衣+長褲套裝,M</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -10766,7 +10766,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】黑色｜上衣+長褲套裝,L</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】豆沙紅｜上衣+長褲套裝,XL</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -10781,7 +10781,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】黑色｜上衣+長褲套裝,M</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】黑色｜上衣+長褲套裝,L</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -10796,7 +10796,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】黑色｜上衣+長褲套裝,XL</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】黑色｜上衣+長褲套裝,M</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -10811,7 +10811,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】灰色｜上衣+長褲套裝,L</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】黑色｜上衣+長褲套裝,XL</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -10826,7 +10826,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】灰色｜上衣+長褲套裝,M</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】灰色｜上衣+長褲套裝,L</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -10841,7 +10841,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】灰色｜上衣+長褲套裝,XL</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】灰色｜上衣+長褲套裝,M</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -10856,7 +10856,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】白色｜上衣+長褲套裝,L</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】灰色｜上衣+長褲套裝,XL</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -10871,7 +10871,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】白色｜上衣+長褲套裝,M</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】白色｜上衣+長褲套裝,L</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】白色｜上衣+長褲套裝,XL</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】白色｜上衣+長褲套裝,M</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -10901,7 +10901,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】藏青色｜上衣+長褲套裝,L</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】白色｜上衣+長褲套裝,XL</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -10916,7 +10916,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】藏青色｜上衣+長褲套裝,M</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】藏青色｜上衣+長褲套裝,L</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -10931,7 +10931,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】藏青色｜上衣+長褲套裝,XL</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】藏青色｜上衣+長褲套裝,M</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -10946,7 +10946,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】黑色｜上衣+長褲套裝,L</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】藏青色｜上衣+長褲套裝,XL</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -10961,7 +10961,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】黑色｜上衣+長褲套裝,M</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】黑色｜上衣+長褲套裝,L</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -10976,7 +10976,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】黑色｜上衣+長褲套裝,XL</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】黑色｜上衣+長褲套裝,M</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -10984,26 +10984,14 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
-        <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[黑色XL]</t>
-        </is>
-      </c>
-      <c r="D696" t="inlineStr">
-        <is>
-          <t>HMH02001-BK-XL</t>
-        </is>
-      </c>
-      <c r="E696" t="inlineStr">
-        <is>
-          <t>HMH02001</t>
-        </is>
-      </c>
+      <c r="C696" t="inlineStr"/>
+      <c r="D696" t="inlineStr"/>
+      <c r="E696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::中膚色👉 推薦一般膚偏白晢膚,140克無絨👉 建議10～15℃</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】黑色｜上衣+長褲套裝,XL</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -11011,14 +10999,26 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr"/>
-      <c r="D697" t="inlineStr"/>
-      <c r="E697" t="inlineStr"/>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[黑色XL]</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>HMH02001-BK-XL</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>HMH02001</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::中膚色👉 推薦一般膚偏白晢膚,180克薄絨👉 建議5～10℃</t>
+          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::中膚色👉 推薦一般膚偏白晢膚,140克無絨👉 建議10～15℃</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -11033,7 +11033,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::深膚色👉 熱門自然膚色首選,140克無絨👉 建議10～15℃</t>
+          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::中膚色👉 推薦一般膚偏白晢膚,180克薄絨👉 建議5～10℃</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -11048,7 +11048,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::深膚色👉 熱門自然膚色首選,180克薄絨👉 建議5～10℃</t>
+          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::深膚色👉 熱門自然膚色首選,140克無絨👉 建議10～15℃</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -11063,7 +11063,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::淺膚色👉 推薦白晢膚或帶妝膚,140克無絨👉 建議10～15℃</t>
+          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::深膚色👉 熱門自然膚色首選,180克薄絨👉 建議5～10℃</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -11078,7 +11078,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::淺膚色👉 推薦白晢膚或帶妝膚,180克薄絨👉 建議5～10℃</t>
+          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::淺膚色👉 推薦白晢膚或帶妝膚,140克無絨👉 建議10～15℃</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -11093,7 +11093,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>[零食封口夾・鎖住新鮮]食品保鮮夾 封口夾 密封夾 零食夾 防潮保鮮夾 零食保鮮夾 零食夾子 食物夾 保鮮 防潮 封口::白色｜單個入</t>
+          <t>[零感光腿襪✨雙層無暇自然膚]光腿神器 褲襪 保暖褲襪 秋冬褲襪 刷毛褲襪 膚色 光腿襪::淺膚色👉 推薦白晢膚或帶妝膚,180克薄絨👉 建議5～10℃</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -11108,7 +11108,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>[零食封口夾・鎖住新鮮]食品保鮮夾 封口夾 密封夾 零食夾 防潮保鮮夾 零食保鮮夾 零食夾子 食物夾 保鮮 防潮 封口::紅色｜單個入</t>
+          <t>[零食封口夾・鎖住新鮮]食品保鮮夾 封口夾 密封夾 零食夾 防潮保鮮夾 零食保鮮夾 零食夾子 食物夾 保鮮 防潮 封口::白色｜單個入</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -11123,7 +11123,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>[零食封口夾・鎖住新鮮]食品保鮮夾 封口夾 密封夾 零食夾 防潮保鮮夾 零食保鮮夾 零食夾子 食物夾 保鮮 防潮 封口::綠色｜單個入</t>
+          <t>[零食封口夾・鎖住新鮮]食品保鮮夾 封口夾 密封夾 零食夾 防潮保鮮夾 零食保鮮夾 零食夾子 食物夾 保鮮 防潮 封口::紅色｜單個入</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -11138,7 +11138,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>[零食封口夾・鎖住新鮮]食品保鮮夾 封口夾 密封夾 零食夾 防潮保鮮夾 零食保鮮夾 零食夾子 食物夾 保鮮 防潮 封口::黃色｜單個入</t>
+          <t>[零食封口夾・鎖住新鮮]食品保鮮夾 封口夾 密封夾 零食夾 防潮保鮮夾 零食保鮮夾 零食夾子 食物夾 保鮮 防潮 封口::綠色｜單個入</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -11153,7 +11153,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸手機也能放]手機袋  手機包 鑰匙包 小錢包 隨身小包 可愛錢包::動物派對,11x17.5cm</t>
+          <t>[零食封口夾・鎖住新鮮]食品保鮮夾 封口夾 密封夾 零食夾 防潮保鮮夾 零食保鮮夾 零食夾子 食物夾 保鮮 防潮 封口::黃色｜單個入</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -11168,7 +11168,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸手機也能放]手機袋  手機包 鑰匙包 小錢包 隨身小包 可愛錢包::湖綠大貓,11x17.5cm</t>
+          <t>[韓國防水牛津布🌸手機也能放]手機袋  手機包 鑰匙包 小錢包 隨身小包 可愛錢包::動物派對,11x17.5cm</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -11183,7 +11183,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸手機也能放]手機袋  手機包 鑰匙包 小錢包 隨身小包 可愛錢包::白色熊熊,11x17.5cm</t>
+          <t>[韓國防水牛津布🌸手機也能放]手機袋  手機包 鑰匙包 小錢包 隨身小包 可愛錢包::湖綠大貓,11x17.5cm</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -11198,7 +11198,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸手機也能放]手機袋  手機包 鑰匙包 小錢包 隨身小包 可愛錢包::白色貓咪,11x17.5cm</t>
+          <t>[韓國防水牛津布🌸手機也能放]手機袋  手機包 鑰匙包 小錢包 隨身小包 可愛錢包::白色熊熊,11x17.5cm</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -11213,7 +11213,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸手機也能放]手機袋  手機包 鑰匙包 小錢包 隨身小包 可愛錢包::白色鳥語,11x17.5cm</t>
+          <t>[韓國防水牛津布🌸手機也能放]手機袋  手機包 鑰匙包 小錢包 隨身小包 可愛錢包::白色貓咪,11x17.5cm</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -11228,7 +11228,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::動物派對,8x11.5x4cm🚫放不下手機</t>
+          <t>[韓國防水牛津布🌸手機也能放]手機袋  手機包 鑰匙包 小錢包 隨身小包 可愛錢包::白色鳥語,11x17.5cm</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -11243,7 +11243,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::新色🆕白色熊熊,8x11.5x4cm🚫放不下手機</t>
+          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::動物派對,8x11.5x4cm🚫放不下手機</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -11258,7 +11258,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::白色貓咪,8x11.5x4cm🚫放不下手機</t>
+          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::新色🆕白色熊熊,8x11.5x4cm🚫放不下手機</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -11273,7 +11273,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::白色鳥語,8x11.5x4cm🚫放不下手機</t>
+          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::白色貓咪,8x11.5x4cm🚫放不下手機</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -11288,7 +11288,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::粉紅小兔,8x11.5x4cm🚫放不下手機</t>
+          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::白色鳥語,8x11.5x4cm🚫放不下手機</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -11303,7 +11303,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::紅色柴犬,8x11.5x4cm🚫放不下手機</t>
+          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::粉紅小兔,8x11.5x4cm🚫放不下手機</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -11318,7 +11318,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::黃色小鴨,8x11.5x4cm🚫放不下手機</t>
+          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::紅色柴犬,8x11.5x4cm🚫放不下手機</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -11333,7 +11333,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::黑色格紋（⚠️隨機格紋）,8x11.5x4cm🚫放不下手機</t>
+          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::黃色小鴨,8x11.5x4cm🚫放不下手機</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -11348,7 +11348,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>[韓系氣質爆棚✨穿出慵懶隨性美] 短袖洋裝 長版上衣 長版T恤 休閒洋裝 孕婦裝夏天 顯瘦洋裝::咖啡色,F</t>
+          <t>[韓國防水牛津布🌸雙層拉鍊]小零錢包 零錢包 小錢包 收納包 可愛零錢包::黑色格紋（⚠️隨機格紋）,8x11.5x4cm🚫放不下手機</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -11363,7 +11363,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>[韓系氣質爆棚✨穿出慵懶隨性美] 短袖洋裝 長版上衣 長版T恤 休閒洋裝 孕婦裝夏天 顯瘦洋裝::白色,F</t>
+          <t>[韓系氣質爆棚✨穿出慵懶隨性美] 短袖洋裝 長版上衣 長版T恤 休閒洋裝 孕婦裝夏天 顯瘦洋裝::咖啡色,F</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -11378,7 +11378,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>[韓系氣質爆棚✨穿出慵懶隨性美] 短袖洋裝 長版上衣 長版T恤 休閒洋裝 孕婦裝夏天 顯瘦洋裝::黑色,F</t>
+          <t>[韓系氣質爆棚✨穿出慵懶隨性美] 短袖洋裝 長版上衣 長版T恤 休閒洋裝 孕婦裝夏天 顯瘦洋裝::白色,F</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -11393,7 +11393,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>[韓系百搭短褲🤍穿出顯瘦腿] 高腰短褲 女短褲 抽繩短褲 A字短褲 顯瘦短褲 運動短褲::粉色,F</t>
+          <t>[韓系氣質爆棚✨穿出慵懶隨性美] 短袖洋裝 長版上衣 長版T恤 休閒洋裝 孕婦裝夏天 顯瘦洋裝::黑色,F</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -11408,7 +11408,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::摩卡色,L</t>
+          <t>[韓系百搭短褲🤍穿出顯瘦腿] 高腰短褲 女短褲 抽繩短褲 A字短褲 顯瘦短褲 運動短褲::粉色,F</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -11423,7 +11423,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::摩卡色,M</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::摩卡色,L</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -11438,7 +11438,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::摩卡色,XL</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::摩卡色,M</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -11453,7 +11453,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::灰湖綠,L</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::摩卡色,XL</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -11468,7 +11468,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::灰湖綠,M</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::灰湖綠,L</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -11483,7 +11483,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::灰湖綠,XL</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::灰湖綠,M</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -11498,7 +11498,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,L</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::灰湖綠,XL</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -11513,7 +11513,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,M</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,L</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -11528,7 +11528,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,XL</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,M</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -11543,7 +11543,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::米咖色,L</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::煙粉色,XL</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -11558,7 +11558,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::米咖色,M</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::米咖色,L</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -11573,7 +11573,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::米咖色,XL</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::米咖色,M</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -11588,7 +11588,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::紫羅蘭,L</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::米咖色,XL</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -11603,7 +11603,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::紫羅蘭,M</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::紫羅蘭,L</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -11618,7 +11618,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::紫羅蘭,XL</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::紫羅蘭,M</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -11633,7 +11633,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::黑色,L</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::紫羅蘭,XL</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -11648,7 +11648,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::黑色,M</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::黑色,L</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -11663,7 +11663,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::黑色,XL</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::黑色,M</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -11678,7 +11678,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>[高雅送禮首選🎁精美DIY禮盒30顆組]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶 紅糖::【原味 x 30顆】蜜糖粉🩷,自行DIY組裝👍推薦選擇</t>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女::黑色,XL</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -11693,7 +11693,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>[高雅送禮首選🎁精美DIY禮盒30顆組]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶 紅糖::【紅棗桂圓 x 30顆】玫瑰紅❤️,自行DIY組裝👍推薦選擇</t>
+          <t>[高雅送禮首選🎁精美DIY禮盒30顆組]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶 紅糖::【原味 x 30顆】蜜糖粉🩷,自行DIY組裝👍推薦選擇</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>[高雅送禮首選🎁精美DIY禮盒30顆組]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶 紅糖::【老薑 x 30顆】玫瑰紅❤️,自行DIY組裝👍推薦選擇</t>
+          <t>[高雅送禮首選🎁精美DIY禮盒30顆組]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶 紅糖::【紅棗桂圓 x 30顆】玫瑰紅❤️,自行DIY組裝👍推薦選擇</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -11723,7 +11723,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>[高雅送禮首選🎁精美DIY禮盒30顆組]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶 紅糖::【老薑 x 30顆】香檳金💛,店家代組裝</t>
+          <t>[高雅送禮首選🎁精美DIY禮盒30顆組]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶 紅糖::【老薑 x 30顆】玫瑰紅❤️,自行DIY組裝👍推薦選擇</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -11738,7 +11738,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>[高雅送禮首選🎁精美DIY禮盒30顆組]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶 紅糖::【老薑 x 30顆】香檳金💛,自行DIY組裝👍推薦選擇</t>
+          <t>[高雅送禮首選🎁精美DIY禮盒30顆組]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶 紅糖::【老薑 x 30顆】香檳金💛,店家代組裝</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -11753,7 +11753,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>[𝐶𝐻𝐼𝐸𝑀𝐼 冬天也要假光腿] 光腿絲襪 透膚絲襪 光腿神器 刷毛褲襪 保暖褲襪 透膚 加絨 假透膚 黑色 冬天 保暖::【全襪款】假透膚黑,無絨款｜建議15–25°C穿著</t>
+          <t>[高雅送禮首選🎁精美DIY禮盒30顆組]黑糖塊 黑糖 黑糖薑母茶 桂圓紅棗茶 紅糖::【老薑 x 30顆】香檳金💛,自行DIY組裝👍推薦選擇</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -11768,7 +11768,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::原味黑糖塊,【罐裝】400g</t>
+          <t>[𝐶𝐻𝐼𝐸𝑀𝐼 冬天也要假光腿] 光腿絲襪 透膚絲襪 光腿神器 刷毛褲襪 保暖褲襪 透膚 加絨 假透膚 黑色 冬天 保暖::【全襪款】假透膚黑,無絨款｜建議15–25°C穿著</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -11783,7 +11783,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::桂花黑糖塊,【罐裝】400g</t>
+          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::原味黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -11798,7 +11798,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::海燕窩黑糖塊,【罐裝】400g</t>
+          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::桂花黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -11813,7 +11813,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::玫瑰四物黑糖塊,【罐裝】400g</t>
+          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::海燕窩黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -11828,7 +11828,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::紅棗桂圓黑糖塊,【罐裝】400g</t>
+          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::玫瑰四物黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -11843,7 +11843,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::老薑黑糖塊,【罐裝】400g</t>
+          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::紅棗桂圓黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -11858,7 +11858,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>可愛超好搭款🌸經典素色微寬鬆薄款短版長袖上衣 六色｜台灣現貨｜女裝｜上衣｜冬裝｜長袖T恤｜素T｜大學T｜衣服｜短版長T::基本薄版👉湖藍色,F</t>
+          <t>『原廠罐裝👑好評熱銷👑手工熬煮』黑糖塊 黑糖薑母茶 黑糖 桂圓紅棗茶::老薑黑糖塊,【罐裝】400g</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -11873,7 +11873,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>可愛超好搭款🌸經典素色微寬鬆薄款短版長袖上衣 六色｜台灣現貨｜女裝｜上衣｜冬裝｜長袖T恤｜素T｜大學T｜衣服｜短版長T::基本薄版👉灰色,F</t>
+          <t>可愛超好搭款🌸經典素色微寬鬆薄款短版長袖上衣 六色｜台灣現貨｜女裝｜上衣｜冬裝｜長袖T恤｜素T｜大學T｜衣服｜短版長T::基本薄版👉湖藍色,F</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -11888,7 +11888,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>可愛超好搭款🌸經典素色微寬鬆薄款短版長袖上衣 六色｜台灣現貨｜女裝｜上衣｜冬裝｜長袖T恤｜素T｜大學T｜衣服｜短版長T::基本薄版👉鵝黃色,F</t>
+          <t>可愛超好搭款🌸經典素色微寬鬆薄款短版長袖上衣 六色｜台灣現貨｜女裝｜上衣｜冬裝｜長袖T恤｜素T｜大學T｜衣服｜短版長T::基本薄版👉灰色,F</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -11903,7 +11903,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>可愛超好搭款🌸經典素色微寬鬆薄款短版長袖上衣 六色｜台灣現貨｜女裝｜上衣｜冬裝｜長袖T恤｜素T｜大學T｜衣服｜短版長T::基本薄版👉黑色,F</t>
+          <t>可愛超好搭款🌸經典素色微寬鬆薄款短版長袖上衣 六色｜台灣現貨｜女裝｜上衣｜冬裝｜長袖T恤｜素T｜大學T｜衣服｜短版長T::基本薄版👉鵝黃色,F</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -11918,7 +11918,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>台灣現貨🇹🇼成本價出清⭐️罕見日系尺碼標高質感高檔內褲包裝袋 自封袋 夾鏈袋 男女內褲通用 可重複使用 ❌無包含內褲❌::L碼空袋子 ❌無包含內褲❌,100個以下👉 $４/個</t>
+          <t>可愛超好搭款🌸經典素色微寬鬆薄款短版長袖上衣 六色｜台灣現貨｜女裝｜上衣｜冬裝｜長袖T恤｜素T｜大學T｜衣服｜短版長T::基本薄版👉黑色,F</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -11933,7 +11933,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>台灣現貨🇹🇼成本價出清⭐️罕見日系尺碼標高質感高檔內褲包裝袋 自封袋 夾鏈袋 男女內褲通用 可重複使用 ❌無包含內褲❌::M碼空袋子 ❌無包含內褲❌,100個以下👉 $４/個</t>
+          <t>台灣現貨🇹🇼成本價出清⭐️罕見日系尺碼標高質感高檔內褲包裝袋 自封袋 夾鏈袋 男女內褲通用 可重複使用 ❌無包含內褲❌::L碼空袋子 ❌無包含內褲❌,100個以下👉 $４/個</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -11948,7 +11948,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>寬鬆男友風🌸秋冬溫暖內刷毛加絨簡約數字運動風中版長袖上衣｜台灣現貨｜衛衣｜oversize｜大學T｜長袖T恤｜女裝::咖啡色,L</t>
+          <t>台灣現貨🇹🇼成本價出清⭐️罕見日系尺碼標高質感高檔內褲包裝袋 自封袋 夾鏈袋 男女內褲通用 可重複使用 ❌無包含內褲❌::M碼空袋子 ❌無包含內褲❌,100個以下👉 $４/個</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -11963,7 +11963,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>春夏經典舒適百搭可愛圓領條紋短袖T恤｜四色｜短袖上衣｜女裝｜棉質T恤｜棉T｜現貨::黃色,M</t>
+          <t>寬鬆男友風🌸秋冬溫暖內刷毛加絨簡約數字運動風中版長袖上衣｜台灣現貨｜衛衣｜oversize｜大學T｜長袖T恤｜女裝::咖啡色,L</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -11978,7 +11978,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::奶油黃,均碼👉35-39碼適穿</t>
+          <t>春夏經典舒適百搭可愛圓領條紋短袖T恤｜四色｜短袖上衣｜女裝｜棉質T恤｜棉T｜現貨::黃色,M</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -11993,7 +11993,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::淺杏桃,均碼👉35-39碼適穿</t>
+          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::奶油黃,均碼👉35-39碼適穿</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -12008,7 +12008,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::燕麥色,均碼👉35-39碼適穿</t>
+          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::淺杏桃,均碼👉35-39碼適穿</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -12023,7 +12023,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::玫粉色,均碼👉35-39碼適穿</t>
+          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::燕麥色,均碼👉35-39碼適穿</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -12038,7 +12038,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::純白色,均碼👉35-39碼適穿</t>
+          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::玫粉色,均碼👉35-39碼適穿</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -12053,7 +12053,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::純黑色,均碼👉35-39碼適穿</t>
+          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::純白色,均碼👉35-39碼適穿</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -12068,7 +12068,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::薑黃色,均碼👉35-39碼適穿</t>
+          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::純黑色,均碼👉35-39碼適穿</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -12083,7 +12083,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜一件式懶人穿搭☘︎秋冬溫暖刷毛連帽寬鬆長版長袖帽T裙｜連帽洋裝 連身裙 大學T 加絨上衣 長裙::咖啡色,F</t>
+          <t>韓國🇰🇷韓系可愛小清新微捲邊中筒襪｜八色｜女襪｜長筒襪｜踝襪｜棉襪｜長襪｜女生襪子｜韓國襪::薑黃色,均碼👉35-39碼適穿</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -12098,7 +12098,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜一件式懶人穿搭☘︎秋冬溫暖刷毛連帽寬鬆長版長袖帽T裙｜連帽洋裝 連身裙 大學T 加絨上衣 長裙::深藍色,F</t>
+          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜一件式懶人穿搭☘︎秋冬溫暖刷毛連帽寬鬆長版長袖帽T裙｜連帽洋裝 連身裙 大學T 加絨上衣 長裙::咖啡色,F</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -12113,7 +12113,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜一件式懶人穿搭☘︎秋冬溫暖刷毛連帽寬鬆長版長袖帽T裙｜連帽洋裝 連身裙 大學T 加絨上衣 長裙::淺灰色,F</t>
+          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜一件式懶人穿搭☘︎秋冬溫暖刷毛連帽寬鬆長版長袖帽T裙｜連帽洋裝 連身裙 大學T 加絨上衣 長裙::深藍色,F</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -12128,7 +12128,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜一件式懶人穿搭☘︎秋冬薄絨極簡風寬鬆條紋長版長袖連身裙｜內刷毛洋裝 連衣裙 長裙 T恤裙 長T 女裝::白條紋,F</t>
+          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜一件式懶人穿搭☘︎秋冬溫暖刷毛連帽寬鬆長版長袖帽T裙｜連帽洋裝 連身裙 大學T 加絨上衣 長裙::淺灰色,F</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -12143,7 +12143,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜一件式懶人穿搭☘︎秋冬薄絨極簡風寬鬆條紋長版長袖連身裙｜內刷毛洋裝 連衣裙 長裙 T恤裙 長T 女裝::黑條紋,F</t>
+          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜一件式懶人穿搭☘︎秋冬薄絨極簡風寬鬆條紋長版長袖連身裙｜內刷毛洋裝 連衣裙 長裙 T恤裙 長T 女裝::白條紋,F</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -12158,7 +12158,7 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜復古風春秋冬薄款字母印花中長版寬鬆長袖上衣｜三色 長袖TEE 長袖T恤 大學T 衛衣 圓領 女裝::碳灰色,L</t>
+          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜一件式懶人穿搭☘︎秋冬薄絨極簡風寬鬆條紋長版長袖連身裙｜內刷毛洋裝 連衣裙 長裙 T恤裙 長T 女裝::黑條紋,F</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -12173,7 +12173,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜復古風春秋冬薄款字母印花中長版寬鬆長袖上衣｜三色 長袖TEE 長袖T恤 大學T 衛衣 圓領 女裝::雲灰白,XL</t>
+          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜復古風春秋冬薄款字母印花中長版寬鬆長袖上衣｜三色 長袖TEE 長袖T恤 大學T 衛衣 圓領 女裝::碳灰色,L</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -12188,7 +12188,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜秋冬韓風字母印花寬鬆長袖上衣｜三色 長袖TEE 長袖T恤 大學T 衛衣 圓領 女裝::粉色,L</t>
+          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜復古風春秋冬薄款字母印花中長版寬鬆長袖上衣｜三色 長袖TEE 長袖T恤 大學T 衛衣 圓領 女裝::雲灰白,XL</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
@@ -12203,7 +12203,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜秋冬韓風字母印花寬鬆長袖上衣｜三色 長袖TEE 長袖T恤 大學T 衛衣 圓領 女裝::黃色,XL</t>
+          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜秋冬韓風字母印花寬鬆長袖上衣｜三色 長袖TEE 長袖T恤 大學T 衛衣 圓領 女裝::粉色,L</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜超柔軟☁️寬鬆男友風♂雙面絨寬鬆撞色刷毛長袖上衣｜長袖TEE 長袖T恤 大學T 衛衣 圓領 女裝::焦糖棕,F</t>
+          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜秋冬韓風字母印花寬鬆長袖上衣｜三色 長袖TEE 長袖T恤 大學T 衛衣 圓領 女裝::黃色,XL</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -12233,12 +12233,12 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::S ➜建議50-55KG</t>
+          <t>𝗖𝗛𝗜𝗘𝗠𝗜.現貨｜超柔軟☁️寬鬆男友風♂雙面絨寬鬆撞色刷毛長袖上衣｜長袖TEE 長袖T恤 大學T 衛衣 圓領 女裝::焦糖棕,F</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>露天</t>
+          <t>蝦皮</t>
         </is>
       </c>
       <c r="C779" t="inlineStr"/>
@@ -12248,12 +12248,12 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, M</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>官網</t>
+          <t>露天</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, XL ➜建議80-85KG</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, M</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -12278,12 +12278,12 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>::</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>蝦皮</t>
+          <t>官網</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -14859,7 +14859,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-SK-140G×1</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -13374,7 +13374,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-SK-140G×3</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-BK-140G×3</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-SK-180G×3</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-SK-280G×3</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-SK-380G×3</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-SK-140G×3</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-BK-140G×3</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-SK-180G×3</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-BK-180G×3</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-SK-380G×3</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-SK-180G×1</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:HFF02001-SK-280G×1</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -11997,7 +11997,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[炭灰色XL]</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,549 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::咖啡色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::咖啡色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色M]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色XL]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::灰色::M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::灰色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::白色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::白色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色XL]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HME03001-WH-XL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::紫色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HME03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::酒紅色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HME03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨::【白色】吊帶款▶中長版 ❗️微透❗️::L</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨::【白色】吊帶款▶加長版 ❗️微透❗️::L</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【圓領】白色L]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HFA02001-CN-WH-L</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【高領】白色L]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,21 +466,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HME03001-BR-L</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -493,21 +481,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HME03001-BR-XL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -520,21 +496,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HME03001-PB-L</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -547,21 +511,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色M]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HME03001-PB-M</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -574,21 +526,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色XL]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HME03001-PB-XL</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -601,21 +541,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HME03001-GY-M</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -628,21 +556,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HME03001-GY-XL</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -655,21 +571,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HME03001-WH-L</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -682,21 +586,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[白色XL]</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HME03001-WH-XL</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -709,21 +601,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HME03001-PU-XL</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -736,21 +616,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HME03001-DN-L</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -763,21 +631,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HME03001-DN-M</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -790,21 +646,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HME03001-DN-XL</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -817,21 +661,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HME03001-RD-XL</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -844,21 +676,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>HME03001-BK-L</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -871,21 +691,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HME03001-BK-M</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -928,21 +736,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>莫代爾長袖打底上衣[【圓領】白色L]</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>HFA02001-CN-WH-L</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>HFA02001</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -955,21 +751,9 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>莫代爾長袖打底上衣[【高領】白色L]</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>HFA02001-TN-WH-L</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>HFA02001</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -982,21 +766,294 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>素色冰絲女士三角內褲[白色L]</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HFE03001-WH-L</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>HFE03001</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】黑色｜上衣+長褲套裝,XL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[黑色XL]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HMH02001-BK-XL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>HMH02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】灰色｜上衣+長褲套裝,M</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[灰色M]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HFH02001-GY-M</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>HFH02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜立領,XL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【立領】黑色XL]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HFA02001-MN-BK-XL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,M</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>莫代爾打底連身裙[吊帶款/短版/黑色M]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-SH-BK-M</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶短版 ❗️微透❗️,M</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>莫代爾打底連身裙[吊帶款/短版/白色M]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-SH-WH-M</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】黑灰色,XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗深藍色,XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HME03002-ST-DN-XL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】深藍色,XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HME03002-SO-DN-XL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::140克微中絨｜參考穿著溫度15-20℃,膚色</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>裸感厚絨光腿褲襪[膚色140G]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-140G</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>HFF02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜高領,M</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【高領】黑色M]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-BK-M</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>::</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,21 +781,9 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[黑色XL]</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>HMH02001-BK-XL</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>HMH02001</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -808,21 +796,9 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[灰色M]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>HFH02001-GY-M</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>HFH02001</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -835,21 +811,9 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色XL]</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>HFA02001-MN-BK-XL</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>HFA02001</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -862,21 +826,9 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/黑色M]</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>HFC01001-TS-SH-BK-M</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>HFC01001</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -889,21 +841,9 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/白色M]</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>HFC01001-TS-SH-WH-M</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>HFC01001</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -916,21 +856,9 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>HME03002-SO-BK-XL</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>HME03002</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -943,21 +871,9 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>HME03002-ST-DN-XL</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>HME03002</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -970,21 +886,9 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>HME03002-SO-DN-XL</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>HME03002</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -997,21 +901,9 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>裸感厚絨光腿褲襪[膚色140G]</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>HFF02001-SK-140G</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>HFF02001</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1024,21 +916,9 @@
           <t>蝦皮</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色M]</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>HFA02001-TN-BK-M</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>HFA02001</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1054,6 +934,33 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::S ➜建議50-55KG</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色S]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HME03001-BK-S</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,17 +946,59 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色S]</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>HME03001-BK-S</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, M</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>HFE03002-GN-M</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色XL]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HME03001-BK-XL</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>HME03001</t>
         </is>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1004,6 +1004,1167 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::藏藍色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, XL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠XL]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HFE03002-GN-XL</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::米咖色, XL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[米咖色XL]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>HFE03002-BG-XL</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::紫羅蘭, XL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭XL]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HFE03002-PU-XL</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::黑色, XL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[黑色XL]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HFE03002-BK-XL</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::煙粉色, XL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[煙粉色XL]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>HFE03002-PK-XL</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::摩卡色, XL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[摩卡色XL]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>HFE03002-BR-XL</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::丁香紫, XL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[丁香紫XL]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HFE03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::中豆紅, XL</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[中豆紅XL]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HFE03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::膚色, XL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[膚色XL]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HFE03001-SK-XL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::藍灰色, XL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[藍灰色XL]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>HFE03001-BU-XL</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::黑色, XL</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[黑色XL]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>HFE03001-BK-XL</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>西裝襯衫上班族必備💼莫代爾男士柔感打底內搭內衣背心::白色, L</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>莫代爾男士柔感內衣[白色L]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HME03003-WH-L</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>HME03003</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::灰色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HME03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::藏藍色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::紫色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HME03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色M]</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>HME03001-WH-M</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::灰色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色M]</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HME03001-RD-M</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::紫羅蘭, M</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭M]</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HFE03002-PU-M</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::煙粉色, M</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[煙粉色M]</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>HFE03002-PK-M</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::米咖色, M</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[米咖色M]</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>HFE03002-BG-M</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗淺藍色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色XL]</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>HME03002-ST-LB-XL</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗深藍色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>HME03002-ST-DN-XL</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】深藍色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>HME03002-SO-DN-XL</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>男女圓領寬鬆素色長袖大學TEE::深岩灰, XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>男女圓領寬鬆素色長袖大學TEE[深岩灰XL]</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>HGA02001-DGY-XL</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>HGA02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::咖啡色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>IKEA 正版環保購物袋 71公升 76公升::【手提款】71L ➜55x37x35cm</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>IKEA 正版環保購物袋[【手提款】71L]</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>HGI03002-HT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>HGI03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】深藍色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色L]</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>HME03002-SO-DN-L</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色L]</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-L</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::老薑黑糖塊, 18G/顆👉單顆入</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】老薑]</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>YGJ03002-OG</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>YGJ03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::玫瑰四物黑糖塊, 18G/顆👉單顆入</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】玫瑰四物]</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>YGJ03002-RFH</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>YGJ03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::原味黑糖塊, 18G/顆👉單顆入</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】原味]</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>YGJ03002-OR</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>YGJ03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::桂花黑糖塊, 18G/顆👉單顆入</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂花]</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>YGJ03002-OS</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>YGJ03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::桂圓紅棗黑糖塊, 18G/顆👉單顆入</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂圓紅棗]</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>YGJ03002-RDL</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>YGJ03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::海燕窩黑糖塊, 18G/顆👉單顆入</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】海燕窩]</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>YGJ03002-SBN</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>YGJ03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>遮肉超顯瘦🆙春夏經典垂感滑順雪紡九分寬褲｜萬年經典不敗款｜上班休閒都好穿::黑色, M</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>HFB01001-BK-M</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>HFB01001</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>遮肉超顯瘦🆙春夏經典垂感滑順雪紡九分寬褲｜萬年經典不敗款｜上班休閒都好穿::象牙淺灰, S</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>HFB01001-GY-S</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>HFB01001</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,6 +2165,87 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::升級版🆙煙粉色, XL</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::白色, XL</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣::白色, 立領, M</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【立領】白色M]</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>HFA02001-MN-WH-M</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::咖啡色::L ➜建議70-75KG</t>
+          <t>::</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>露天</t>
+          <t>蝦皮</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -473,157 +473,277 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::咖啡色::XL ➜建議80-85KG</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶短版 ❗️微透❗️,M</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>莫代爾打底連身裙[吊帶款/短版/白色M]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-SH-WH-M</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,M</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>莫代爾打底連身裙[吊帶款/短版/黑色M]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-SH-BK-M</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::M ➜建議60-65KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】深藍色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HME03002-SO-DN-XL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::XL ➜建議80-85KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】黑灰色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::灰色::M ➜建議60-65KG</t>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗深藍色,XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HME03002-ST-DN-XL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::灰色::XL ➜建議80-85KG</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜立領,XL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【立領】黑色XL]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HFA02001-MN-BK-XL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::白色::L ➜建議70-75KG</t>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜高領,M</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【高領】黑色M]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-BK-M</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::白色::XL ➜建議80-85KG</t>
+          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::140克微中絨｜參考穿著溫度15-20℃,膚色</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>裸感厚絨光腿褲襪[膚色140G]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-140G</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HFF02001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::紫色::XL ➜建議80-85KG</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】灰色｜上衣+長褲套裝,M</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[灰色M]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HFH02001-GY-M</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HFH02001</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】黑色｜上衣+長褲套裝,XL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>露天</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[黑色XL]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HMH02001-BK-XL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HMH02001</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::M ➜建議60-65KG</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::咖啡色::L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -631,14 +751,26 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::咖啡色::XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -646,14 +778,26 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::酒紅色::XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -661,14 +805,26 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -676,14 +832,26 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色M]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::M ➜建議60-65KG</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -691,14 +859,26 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色XL]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨::【白色】吊帶款▶中長版 ❗️微透❗️::L</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::灰色::M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -706,14 +886,26 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨::【白色】吊帶款▶加長版 ❗️微透❗️::L</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::灰色::XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -721,14 +913,26 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::白色::L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -736,14 +940,26 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::白色::XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -751,14 +967,26 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色XL]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HME03001-WH-XL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::紫色::XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -766,124 +994,220 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HME03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【男款】黑色｜上衣+長褲套裝,XL</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝::【女款】灰色｜上衣+長褲套裝,M</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜立領,XL</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【黑色】吊帶款▶短版,M</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::酒紅色::XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HME03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心::【白色】吊帶款▶短版 ❗️微透❗️,M</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】黑灰色,XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::〖條紋〗深藍色,XL ➜建議80-85KG</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::S ➜建議50-55KG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色S]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HME03001-BK-S</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲::【素色】深藍色,XL ➜建議80-85KG</t>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨::【白色】吊帶款▶中長版 ❗️微透❗️::L</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>蝦皮</t>
+          <t>露天</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -893,12 +1217,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪::140克微中絨｜參考穿著溫度15-20℃,膚色</t>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨::【白色】吊帶款▶加長版 ❗️微透❗️::L</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>蝦皮</t>
+          <t>露天</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -908,37 +1232,61 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣::黑色｜高領,M</t>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【圓領】白色L]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HFA02001-CN-WH-L</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>::</t>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【高領】白色L]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::S ➜建議50-55KG</t>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -946,14 +1294,26 @@
           <t>露天</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, M</t>
+          <t>IKEA 正版環保購物袋 71公升 76公升::【手提款】71L ➜55x37x35cm</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -963,24 +1323,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M]</t>
+          <t>IKEA 正版環保購物袋[【手提款】71L]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HFE03002-GN-M</t>
+          <t>HGI03002-HT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HFE03002</t>
+          <t>HGI03002</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, XL ➜建議80-85KG</t>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::原味黑糖塊, 18G/顆👉單顆入</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -990,24 +1350,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色XL]</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】原味]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>HME03001-BK-XL</t>
+          <t>YGJ03002-OR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>YGJ03002</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, M ➜建議60-65KG</t>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::桂圓紅棗黑糖塊, 18G/顆👉單顆入</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1017,24 +1377,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂圓紅棗]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>HME03001-BK-M</t>
+          <t>YGJ03002-RDL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>YGJ03002</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::藏藍色, M ➜建議60-65KG</t>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::桂花黑糖塊, 18G/顆👉單顆入</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1044,24 +1404,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂花]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HME03001-DN-M</t>
+          <t>YGJ03002-OS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>YGJ03002</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, XL</t>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::海燕窩黑糖塊, 18G/顆👉單顆入</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1071,24 +1431,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠XL]</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】海燕窩]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HFE03002-GN-XL</t>
+          <t>YGJ03002-SBN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HFE03002</t>
+          <t>YGJ03002</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::米咖色, XL</t>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::玫瑰四物黑糖塊, 18G/顆👉單顆入</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1098,24 +1458,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[米咖色XL]</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】玫瑰四物]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>HFE03002-BG-XL</t>
+          <t>YGJ03002-RFH</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HFE03002</t>
+          <t>YGJ03002</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::紫羅蘭, XL</t>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::老薑黑糖塊, 18G/顆👉單顆入</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1125,24 +1485,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭XL]</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】老薑]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>HFE03002-PU-XL</t>
+          <t>YGJ03002-OG</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HFE03002</t>
+          <t>YGJ03002</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::黑色, XL</t>
+          <t>男女圓領寬鬆素色長袖大學TEE::深岩灰, XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1152,24 +1512,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[黑色XL]</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[深岩灰XL]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>HFE03002-BK-XL</t>
+          <t>HGA02001-DGY-XL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HFE03002</t>
+          <t>HGA02001</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::煙粉色, XL</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::升級版🆙煙粉色, XL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1179,17 +1539,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[煙粉色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>HFE03002-PK-XL</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HFE03002</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1583,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::丁香紫, XL</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, M</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1233,24 +1593,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[丁香紫XL]</t>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HFE03001-PU-XL</t>
+          <t>HFE03002-GN-M</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HFE03001</t>
+          <t>HFE03002</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::中豆紅, XL</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, XL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1260,24 +1620,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[中豆紅XL]</t>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠XL]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HFE03001-RD-XL</t>
+          <t>HFE03002-GN-XL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HFE03001</t>
+          <t>HFE03002</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::膚色, XL</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::煙粉色, M</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1287,24 +1647,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[膚色XL]</t>
+          <t>舒適寬邊莫代爾女士三角內褲[煙粉色M]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HFE03001-SK-XL</t>
+          <t>HFE03002-PK-M</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HFE03001</t>
+          <t>HFE03002</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::藍灰色, XL</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::煙粉色, XL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1314,24 +1674,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[藍灰色XL]</t>
+          <t>舒適寬邊莫代爾女士三角內褲[煙粉色XL]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>HFE03001-BU-XL</t>
+          <t>HFE03002-PK-XL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HFE03001</t>
+          <t>HFE03002</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::黑色, XL</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::米咖色, M</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1341,24 +1701,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[黑色XL]</t>
+          <t>舒適寬邊莫代爾女士三角內褲[米咖色M]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>HFE03001-BK-XL</t>
+          <t>HFE03002-BG-M</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HFE03001</t>
+          <t>HFE03002</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>西裝襯衫上班族必備💼莫代爾男士柔感打底內搭內衣背心::白色, L</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::米咖色, XL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1368,24 +1728,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[白色L]</t>
+          <t>舒適寬邊莫代爾女士三角內褲[米咖色XL]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>HME03003-WH-L</t>
+          <t>HFE03002-BG-XL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HME03003</t>
+          <t>HFE03002</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::灰色, XL ➜建議80-85KG</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::紫羅蘭, M</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1395,24 +1755,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
+          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭M]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HME03001-GY-XL</t>
+          <t>HFE03002-PU-M</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>HFE03002</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, XL ➜建議80-85KG</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::紫羅蘭, XL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1422,24 +1782,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
+          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭XL]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>HME03001-RD-XL</t>
+          <t>HFE03002-PU-XL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>HFE03002</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::藏藍色, XL ➜建議80-85KG</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::黑色, XL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1449,24 +1809,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
+          <t>舒適寬邊莫代爾女士三角內褲[黑色XL]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>HME03001-DN-XL</t>
+          <t>HFE03002-BK-XL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>HFE03002</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::紫色, XL ➜建議80-85KG</t>
+          <t>秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣::白色, 立領, M</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1476,24 +1836,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
+          <t>莫代爾長袖打底上衣[【立領】白色M]</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>HME03001-PU-XL</t>
+          <t>HFA02001-MN-WH-M</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>HFA02001</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
+          <t>西裝襯衫上班族必備💼莫代爾男士柔感打底內搭內衣背心::白色, L</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1503,24 +1863,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+          <t>莫代爾男士柔感內衣[白色L]</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>HME03001-BK-L</t>
+          <t>HME03003-WH-L</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>HME03003</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】深藍色, L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1530,24 +1890,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色L]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HME03001-WH-L</t>
+          <t>HME03002-SO-DN-L</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>HME03002</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】深藍色, XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1557,24 +1917,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色M]</t>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>HME03001-WH-M</t>
+          <t>HME03002-SO-DN-XL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>HME03002</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::灰色, M ➜建議60-65KG</t>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1584,24 +1944,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色L]</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HME03001-GY-M</t>
+          <t>HME03002-SO-BK-L</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>HME03002</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, M ➜建議60-65KG</t>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1611,24 +1971,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[酒紅色M]</t>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HME03001-RD-M</t>
+          <t>HME03002-SO-BK-XL</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HME03001</t>
+          <t>HME03002</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::紫羅蘭, M</t>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗深藍色, XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1638,24 +1998,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭M]</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HFE03002-PU-M</t>
+          <t>HME03002-ST-DN-XL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HFE03002</t>
+          <t>HME03002</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::煙粉色, M</t>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗淺藍色, XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1665,24 +2025,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[煙粉色M]</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色XL]</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HFE03002-PK-M</t>
+          <t>HME03002-ST-LB-XL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HFE03002</t>
+          <t>HME03002</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::米咖色, M</t>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::丁香紫, XL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1692,24 +2052,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[米咖色M]</t>
+          <t>素色冰絲女士三角內褲[丁香紫XL]</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HFE03002-BG-M</t>
+          <t>HFE03001-PU-XL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>HFE03002</t>
+          <t>HFE03001</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, XL ➜建議80-85KG</t>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::中豆紅, XL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1719,24 +2079,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
+          <t>素色冰絲女士三角內褲[中豆紅XL]</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>HME03002-SO-BK-XL</t>
+          <t>HFE03001-RD-XL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>HME03002</t>
+          <t>HFE03001</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗淺藍色, XL ➜建議80-85KG</t>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::白色, XL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1746,24 +2106,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>HME03002-ST-LB-XL</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>HME03002</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗深藍色, XL ➜建議80-85KG</t>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::膚色, XL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1773,24 +2133,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
+          <t>素色冰絲女士三角內褲[膚色XL]</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>HME03002-ST-DN-XL</t>
+          <t>HFE03001-SK-XL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HME03002</t>
+          <t>HFE03001</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】深藍色, XL ➜建議80-85KG</t>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::藍灰色, XL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1800,24 +2160,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
+          <t>素色冰絲女士三角內褲[藍灰色XL]</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>HME03002-SO-DN-XL</t>
+          <t>HFE03001-BU-XL</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HME03002</t>
+          <t>HFE03001</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE::深岩灰, XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::黑色, XL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1827,17 +2187,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[深岩灰XL]</t>
+          <t>素色冰絲女士三角內褲[黑色XL]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>HGA02001-DGY-XL</t>
+          <t>HFE03001-BK-XL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>HGA02001</t>
+          <t>HFE03001</t>
         </is>
       </c>
     </row>
@@ -1871,7 +2231,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IKEA 正版環保購物袋 71公升 76公升::【手提款】71L ➜55x37x35cm</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::灰色, M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1881,24 +2241,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IKEA 正版環保購物袋[【手提款】71L]</t>
+          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>HGI03002-HT</t>
+          <t>HME03001-GY-M</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HGI03002</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】深藍色, L ➜建議70-75KG</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::灰色, XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1908,24 +2268,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】深藍色L]</t>
+          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>HME03002-SO-DN-L</t>
+          <t>HME03001-GY-XL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HME03002</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, L ➜建議70-75KG</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1935,24 +2295,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】黑灰色L]</t>
+          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>HME03002-SO-BK-L</t>
+          <t>HME03001-WH-L</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>HME03002</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::老薑黑糖塊, 18G/顆👉單顆入</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1962,24 +2322,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】老薑]</t>
+          <t>超薄裸感冰絲男士四角內褲[白色M]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>YGJ03002-OG</t>
+          <t>HME03001-WH-M</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>YGJ03002</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::玫瑰四物黑糖塊, 18G/顆👉單顆入</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::紫色, XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1989,24 +2349,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】玫瑰四物]</t>
+          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>YGJ03002-RFH</t>
+          <t>HME03001-PU-XL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>YGJ03002</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::原味黑糖塊, 18G/顆👉單顆入</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::藏藍色, M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2016,24 +2376,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】原味]</t>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>YGJ03002-OR</t>
+          <t>HME03001-DN-M</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>YGJ03002</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::桂花黑糖塊, 18G/顆👉單顆入</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::藏藍色, XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2043,24 +2403,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂花]</t>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>YGJ03002-OS</t>
+          <t>HME03001-DN-XL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>YGJ03002</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::桂圓紅棗黑糖塊, 18G/顆👉單顆入</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2070,24 +2430,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂圓紅棗]</t>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色M]</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>YGJ03002-RDL</t>
+          <t>HME03001-RD-M</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>YGJ03002</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::海燕窩黑糖塊, 18G/顆👉單顆入</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2097,24 +2457,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】海燕窩]</t>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>YGJ03002-SBN</t>
+          <t>HME03001-RD-XL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>YGJ03002</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>遮肉超顯瘦🆙春夏經典垂感滑順雪紡九分寬褲｜萬年經典不敗款｜上班休閒都好穿::黑色, M</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2124,24 +2484,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>HFB01001-BK-M</t>
+          <t>HME03001-BK-L</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HFB01001</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>遮肉超顯瘦🆙春夏經典垂感滑順雪紡九分寬褲｜萬年經典不敗款｜上班休閒都好穿::象牙淺灰, S</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2151,24 +2511,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>HFB01001-GY-S</t>
+          <t>HME03001-BK-M</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HFB01001</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::升級版🆙煙粉色, XL</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2178,24 +2538,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[黑色XL]</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>HME03001-BK-XL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::白色, XL</t>
+          <t>遮肉超顯瘦🆙春夏經典垂感滑順雪紡九分寬褲｜萬年經典不敗款｜上班休閒都好穿::象牙淺灰, S</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2210,19 +2570,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>HFB01001-GY-S</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>HFB01001</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣::白色, 立領, M</t>
+          <t>遮肉超顯瘦🆙春夏經典垂感滑順雪紡九分寬褲｜萬年經典不敗款｜上班休閒都好穿::黑色, M</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2232,17 +2592,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>HFA02001-MN-WH-M</t>
+          <t>HFB01001-BK-M</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>HFA02001</t>
+          <t>HFB01001</t>
         </is>
       </c>
     </row>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,557 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨::【白色】吊帶款▶中長版 ❗️微透❗️::L</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨::【白色】吊帶款▶加長版 ❗️微透❗️::L</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::黑色::M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色M]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::灰色::M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::白色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::咖啡色::L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::寶藍色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色XL]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::咖啡色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::酒紅色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HME03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::藏藍色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::紫色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HME03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::灰色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲::白色::XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色XL]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HME03001-WH-XL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜高領::L</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【高領】白色L]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE::白色｜圓領::L</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣[【圓領】白色L]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HFA02001-CN-WH-L</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨::白色::L</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E636"/>
+  <dimension ref="A1:E672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12400,19 +12400,11 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】老薑]</t>
-        </is>
-      </c>
-      <c r="D630" t="inlineStr">
-        <is>
-          <t>YGJ03002-OG</t>
-        </is>
-      </c>
-      <c r="E630" t="inlineStr">
-        <is>
-          <t>YGJ03002</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr"/>
+      <c r="E630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -12427,19 +12419,11 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
-        </is>
-      </c>
-      <c r="D631" t="inlineStr">
-        <is>
-          <t>HME03001-PB-L</t>
-        </is>
-      </c>
-      <c r="E631" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr"/>
+      <c r="E631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -12454,19 +12438,11 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
-        </is>
-      </c>
-      <c r="D632" t="inlineStr">
-        <is>
-          <t>HME03001-BR-L</t>
-        </is>
-      </c>
-      <c r="E632" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr"/>
+      <c r="E632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -12481,19 +12457,11 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色L]</t>
-        </is>
-      </c>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>HME03001-GY-L</t>
-        </is>
-      </c>
-      <c r="E633" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr"/>
+      <c r="E633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -12508,19 +12476,11 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[酒紅色L]</t>
-        </is>
-      </c>
-      <c r="D634" t="inlineStr">
-        <is>
-          <t>HME03001-RD-L</t>
-        </is>
-      </c>
-      <c r="E634" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr"/>
+      <c r="E634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -12535,19 +12495,11 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
-        </is>
-      </c>
-      <c r="D635" t="inlineStr">
-        <is>
-          <t>HME03001-BK-L</t>
-        </is>
-      </c>
-      <c r="E635" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr"/>
+      <c r="E635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -12562,15 +12514,979 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色S]</t>
-        </is>
-      </c>
-      <c r="D636" t="inlineStr">
-        <is>
-          <t>HME03001-BK-S</t>
-        </is>
-      </c>
-      <c r="E636" t="inlineStr">
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr"/>
+      <c r="E636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗淺藍色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色XL]</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>HME03002-ST-LB-XL</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗深藍色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>HME03002-ST-DN-XL</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】深藍色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>HME03002-SO-DN-XL</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>男女圓領寬鬆素色長袖大學TEE::深岩灰, XL ➜建議𝟴𝟬-𝟵𝟱𝗞𝗚</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>男女圓領寬鬆素色長袖大學TEE[深岩灰XL]</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>HGA02001-DGY-XL</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>HGA02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::藏藍色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::灰色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::咖啡色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色XL]</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>HME03001-BK-XL</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>IKEA 正版環保購物袋 71公升 76公升::【手提款】71L ➜55x37x35cm</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>IKEA 正版環保購物袋[【手提款】71L]</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>HGI03002-HT</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>HGI03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】深藍色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色L]</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>HME03002-SO-DN-L</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色L]</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-L</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色M]</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>HME03001-RD-M</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::黑色, M</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[黑色M]</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>HFE03001-BK-M</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗黑灰色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】黑灰色XL]</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>HME03002-ST-BK-XL</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】淺灰色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】淺灰色XL]</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>HME03002-SO-GY-XL</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::黑色, L</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>HFE03001-BK-L</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::丁香紫, XL</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[丁香紫XL]</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>HFE03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::中豆紅, XL</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[中豆紅XL]</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>HFE03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>超舒適零觸感冰絲內褲❄涼感高彈力純棉中腰三角內褲::藍灰色, XL</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲[藍灰色XL]</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>HFE03001-BU-XL</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::老薑黑糖塊, 18G/顆👉單顆入</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】老薑]</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>YGJ03002-OG</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>YGJ03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::原味黑糖塊, 18G/顆👉單顆入</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】原味]</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>YGJ03002-OR</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>YGJ03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑臺灣天然養生手工黑糖塊::桂圓紅棗黑糖塊, 18G/顆👉單顆入</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂圓紅棗]</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>YGJ03002-RDL</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>YGJ03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗深藍色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色M]</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>HME03002-ST-DN-M</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗黑灰色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】黑灰色M]</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>HME03002-ST-BK-M</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗深藍色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色L]</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>HME03002-ST-DN-L</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::〖條紋〗黑灰色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【條紋】黑灰色L]</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>HME03002-ST-BK-L</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色M]</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>HME03001-WH-M</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::灰色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色L]</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>HME03001-GY-L</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::咖啡色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色L]</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>HME03001-RD-L</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::紫色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[紫色L]</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>HME03001-PU-L</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::藏藍色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::寶藍色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
         <is>
           <t>HME03001</t>
         </is>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E852"/>
+  <dimension ref="A1:E864"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16352,19 +16352,11 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
-        </is>
-      </c>
-      <c r="D838" t="inlineStr">
-        <is>
-          <t>HME03001-PB-L</t>
-        </is>
-      </c>
-      <c r="E838" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr"/>
+      <c r="E838" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -16379,19 +16371,11 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
-        </is>
-      </c>
-      <c r="D839" t="inlineStr">
-        <is>
-          <t>HME03001-DN-L</t>
-        </is>
-      </c>
-      <c r="E839" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr"/>
+      <c r="E839" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -16406,19 +16390,11 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
-        </is>
-      </c>
-      <c r="D840" t="inlineStr">
-        <is>
-          <t>HME03001-BK-L</t>
-        </is>
-      </c>
-      <c r="E840" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr"/>
+      <c r="E840" t="inlineStr"/>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
@@ -16433,19 +16409,11 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
-        </is>
-      </c>
-      <c r="D841" t="inlineStr">
-        <is>
-          <t>HME03001-WH-L</t>
-        </is>
-      </c>
-      <c r="E841" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr"/>
+      <c r="E841" t="inlineStr"/>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -16460,19 +16428,11 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
-        </is>
-      </c>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>HME03001-BR-L</t>
-        </is>
-      </c>
-      <c r="E842" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr"/>
+      <c r="E842" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -16487,19 +16447,11 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色XL]</t>
-        </is>
-      </c>
-      <c r="D843" t="inlineStr">
-        <is>
-          <t>HME03001-PB-XL</t>
-        </is>
-      </c>
-      <c r="E843" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr"/>
+      <c r="E843" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -16514,19 +16466,11 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
-        </is>
-      </c>
-      <c r="D844" t="inlineStr">
-        <is>
-          <t>HME03001-BR-XL</t>
-        </is>
-      </c>
-      <c r="E844" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr"/>
+      <c r="E844" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -16541,19 +16485,11 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
-        </is>
-      </c>
-      <c r="D845" t="inlineStr">
-        <is>
-          <t>HME03001-RD-XL</t>
-        </is>
-      </c>
-      <c r="E845" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr"/>
+      <c r="E845" t="inlineStr"/>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -16568,19 +16504,11 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
-        </is>
-      </c>
-      <c r="D846" t="inlineStr">
-        <is>
-          <t>HME03001-DN-XL</t>
-        </is>
-      </c>
-      <c r="E846" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr"/>
+      <c r="E846" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -16595,19 +16523,11 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
-        </is>
-      </c>
-      <c r="D847" t="inlineStr">
-        <is>
-          <t>HME03001-PU-XL</t>
-        </is>
-      </c>
-      <c r="E847" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr"/>
+      <c r="E847" t="inlineStr"/>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -16622,19 +16542,11 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
-        </is>
-      </c>
-      <c r="D848" t="inlineStr">
-        <is>
-          <t>HME03001-GY-XL</t>
-        </is>
-      </c>
-      <c r="E848" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr"/>
+      <c r="E848" t="inlineStr"/>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -16649,19 +16561,11 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色XL]</t>
-        </is>
-      </c>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>HME03001-WH-XL</t>
-        </is>
-      </c>
-      <c r="E849" t="inlineStr">
-        <is>
-          <t>HME03001</t>
-        </is>
-      </c>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr"/>
+      <c r="E849" t="inlineStr"/>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -16679,16 +16583,8 @@
           <t>未匹配</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr">
-        <is>
-          <t>HFA02001-WH_TN-L</t>
-        </is>
-      </c>
-      <c r="E850" t="inlineStr">
-        <is>
-          <t>HFA02001</t>
-        </is>
-      </c>
+      <c r="D850" t="inlineStr"/>
+      <c r="E850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -16706,16 +16602,8 @@
           <t>未匹配</t>
         </is>
       </c>
-      <c r="D851" t="inlineStr">
-        <is>
-          <t>HFA02001-WH_CN-L</t>
-        </is>
-      </c>
-      <c r="E851" t="inlineStr">
-        <is>
-          <t>HFA02001</t>
-        </is>
-      </c>
+      <c r="D851" t="inlineStr"/>
+      <c r="E851" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -16730,17 +16618,333 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[白色L]</t>
-        </is>
-      </c>
-      <c r="D852" t="inlineStr">
-        <is>
-          <t>HFE03001-WH-L</t>
-        </is>
-      </c>
-      <c r="E852" t="inlineStr">
-        <is>
-          <t>HFE03001</t>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr"/>
+      <c r="E852" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[白色M]</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>HME03001-WH-M</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::灰色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色M]</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>HME03001-RD-M</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::藏藍色, M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, M</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M]</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>HFE03002-GN-M</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::紫羅蘭, M</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭M]</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>HFE03002-PU-M</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::煙粉色, M</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[煙粉色M]</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>HFE03002-PK-M</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::米咖色, M</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>舒適寬邊莫代爾女士三角內褲[米咖色M]</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>HFE03002-BG-M</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>HME03002</t>
         </is>
       </c>
     </row>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>街頭風NO字母五分袖T恤裙[灰色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IKEA 正版環保購物袋[【手提款】71L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】粉色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】霧藍L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>保暖超厚絨中筒羊絨襪[黑色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>台灣美肌超薄透膚絲襪[基本黑]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>台灣美肌超薄透膚絲襪[白皙膚]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>台灣美肌超薄透膚絲襪[自然膚]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[丁香紫L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[丁香紫M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[丁香紫XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[中豆紅L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[中豆紅M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[中豆紅XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[膚色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[膚色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[膚色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[藍灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[藍灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[藍灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>素色莫代爾V領短袖T[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>筆筒文具多功能桌面收纳盒[粉色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>筆筒文具多功能桌面收纳盒[藍色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>鵝卵石造型免釘無痕黏貼掛勾[米黃色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】原味]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂圓紅棗]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂花]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】海燕窩]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】玫瑰四物]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】老薑]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>溫暖刷毛高腰修身鯊魚微喇叭褲[深灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>溫暖刷毛高腰修身鯊魚微喇叭褲[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>溫暖刷毛高腰修身鯊魚微喇叭褲[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>毛呢舒適鬆緊腰百褶短裙[咖啡色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>毛呢舒適鬆緊腰百褶短裙[深灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>毛呢舒適鬆緊腰百褶短裙[深灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>毛呢舒適鬆緊腰百褶短裙[深灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>毛呢舒適鬆緊腰百褶短裙[米白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>毛呢舒適鬆緊腰百褶短裙[米白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>長絨棉針織堆堆襪套[卡其色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>長絨棉針織堆堆襪套[咖啡色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>長絨棉針織堆堆襪套[奶白色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>長絨棉針織堆堆襪套[淺粉色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>長絨棉針織堆堆襪套[白色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>長絨棉針織堆堆襪套[黑色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[紫色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[紫色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[紫色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[酒紅色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[酒紅色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>台灣製冰絲涼感防曬袖套[【平口款】深灰色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>台灣製冰絲涼感防曬袖套[【平口款】藏藍色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>台灣製冰絲涼感防曬袖套[【平口款】黑色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>台灣製冰絲涼感防曬袖套[【露指款】深灰色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>台灣製冰絲涼感防曬袖套[【露指款】藏藍色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>台灣製冰絲涼感防曬袖套[【露指款】黑色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>台灣製強力高彈輕量褲襪[亮膚色140G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>台灣製強力高彈輕量褲襪[亮膚色30G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>台灣製強力高彈輕量褲襪[亮膚色50G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>台灣製強力高彈輕量褲襪[深膚色140G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>台灣製強力高彈輕量褲襪[深膚色30G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>台灣製強力高彈輕量褲襪[深膚色50G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>台灣製強力高彈輕量褲襪[黑色140G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>台灣製強力高彈輕量褲襪[黑色30G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>台灣製強力高彈輕量褲襪[黑色50G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/中長/灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/中長/灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/中長/灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/加長/灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/中長/白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/中長/白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/中長/白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/加長/白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/加長/白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/中長/黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/中長/黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/加長/黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/加長/黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[吊帶款/短版/黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/中長/灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/中長/灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/中長/灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/短版/灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/短版/灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/中長/白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/中長/白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/中長/白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/短版/白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/短版/白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/短版/白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/中長/黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/中長/黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/中長/黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/短版/黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/短版/黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>莫代爾打底連身裙[背心款/短版/黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>大容量PVC防水收納包[【拉鍊款】米白色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】原味]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】桂花]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】海燕窩]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】玫瑰四物]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】紅棗桂圓]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】老薑]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【中領】月光灰L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【中領】月光灰S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【中領】月光灰XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【圓領】月光灰L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【圓領】月光灰M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【圓領】月光灰XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【中領】珊瑚粉M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【中領】珊瑚粉XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【圓領】珊瑚粉M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【圓領】珊瑚粉S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【中領】神秘黑L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【中領】神秘黑M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【中領】神秘黑S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【中領】神秘黑XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【圓領】神秘黑L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【圓領】神秘黑S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【圓領】神秘黑XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【中領】經典膚S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【中領】經典膚XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【圓領】經典膚L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>德絨保暖打底長袖上衣[【圓領】經典膚M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[沙粉色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[黑色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>（女款）情侶款珊瑚絨家居圓領睡衣+睡褲套裝[米白色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>（男款）情侶款珊瑚絨家居圓領睡衣+睡褲套裝[深灰色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【細肩帶】白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【細肩帶】白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【細肩帶】膚色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【細肩帶】膚色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【細肩帶】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【細肩帶】黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【寬肩帶】灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【寬肩帶】白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【寬肩帶】白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【寬肩帶】膚色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【寬肩帶】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>輕薄莫代爾打底背心[【寬肩帶】黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>超防掉隱形PRO無肩帶內衣[乳白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>超防掉隱形PRO無肩帶內衣[乳白色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>超防掉隱形PRO無肩帶內衣[優雅黑L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>超防掉隱形PRO無肩帶內衣[粉底膚S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[冰川白L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[冰川白M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[奶咖色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[奶咖色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[奶咖色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[奶油黃L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[奶油黃M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[奶油黃XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[薄荷綠L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[薄荷綠M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[薄荷綠XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[輕氧藍L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[輕氧藍M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[輕氧藍XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[雅黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[雅黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>冰絲面膜速乾三角內褲[雅黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>黑繃帶高腰收腹三角內褲[楓木色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>黑繃帶高腰收腹三角內褲[綠蘿紗F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>黑繃帶高腰收腹三角內褲[綠蘿紗XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>黑繃帶高腰收腹三角內褲[羊毛色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>黑繃帶高腰收腹三角內褲[羊毛色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>黑繃帶高腰收腹三角內褲[肉桂粉F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>黑繃帶高腰收腹三角內褲[肉桂粉XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>黑繃帶高腰收腹三角內褲[黑色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】深藍色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】深藍色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】深藍色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】淺灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】淺灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】淺灰色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】淺灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】淺綠色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】淺綠色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】淺綠色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】淺綠色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】黑灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】黑灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】黑灰色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】深藍色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】深藍色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】深藍色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】淺灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】淺灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】淺灰色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】淺灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】黑灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】黑灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】黑灰色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【條紋】黑灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[2倍厚A罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[2倍厚B罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[2倍厚C罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[2倍厚D罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[4倍厚A罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[4倍厚B罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[4倍厚C罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[4倍厚D罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[立體杯A罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[立體杯B罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[立體杯C罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>水感防掉💧隱形矽膠胸貼[立體杯D罩杯]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>M型短頸膚感防滑衣架[奶霧灰]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>M型短頸膚感防滑衣架[燕麥白]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>可愛動物眼鏡保護收納掛袋[棕色小熊]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>可愛動物眼鏡保護收納掛袋[灰白小貓]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>可愛動物眼鏡保護收納掛袋[黃白小貓]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>日式可摺疊輕量保溫便當袋[可可棕]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>日式可摺疊輕量保溫便當袋[大象灰]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>皮質化妝保養品旅行收納包[灰藕粉L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>站立式化妝刷具旅行收納包[卡其色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>旅行衣物分裝收納整理袋[米色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>旅行衣物分裝收納整理袋[粉色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>旅行衣物分裝收納整理袋[藍色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>旅行衣物分裝收納整理袋[黑色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>分層萬用小物收納網格袋[燕麥色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -10810,7 +10810,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>分層萬用小物收納網格袋[燕麥色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>分層萬用小物收納網格袋[燕麥色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>分層萬用小物收納網格袋[藍灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>分層萬用小物收納網格袋[藍灰色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>旅行摺疊曬衣夾[碧波紋]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>隱形不透款無痕內衣[【寬肩帶】深膚色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>隱形不透款無痕內衣[【寬肩帶】深膚色XXL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>隱形不透款無痕內衣[【細肩帶】抹茶綠XXL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>隱形不透款無痕內衣[【細肩帶】淺膚色XXL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>溫柔韓系長版針織外套[摩卡棕F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】淺卡其L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】淺卡其M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】淺卡其XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】淺卡其M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】淺卡其M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】淺卡其XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】灰色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】灰色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】白色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】粉色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】粉色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】粉色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】粉色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】粉色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】粉色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】霧藍L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】霧藍XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】霧藍L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】霧藍S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】霧藍XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】霧藍M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】霧藍XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】黑色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>羅紋長袖打底上衣[咖啡色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>羅紋長袖打底上衣[灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>羅紋長袖打底上衣[灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>羅紋長袖打底上衣[白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>羅紋長袖打底上衣[白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>羅紋長袖打底上衣[薄荷綠M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>羅紋長袖打底上衣[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>羅紋長袖打底上衣[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>羅紋長袖打底上衣[黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】淺卡其L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -14822,7 +14822,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】粉色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】霧藍XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -14957,7 +14957,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】霧藍XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】霧藍M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -15065,7 +15065,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[沙粉色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[沙粉色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[沙粉色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[沙粉色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[深岩灰L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[深岩灰M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[深岩灰XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[深海藍L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[深海藍S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[深海藍XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[白色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[麻灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[麻灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[麻灰色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[麻灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[黑色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>男女圓領寬鬆素色長袖大學TEE[黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[膚色140G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[黑色140G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[膚色180G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[黑色180G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[膚色280G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[黑色280G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[膚色380G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[黑色380G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[膚色140G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[黑色140G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[膚色180G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[黑色180G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[膚色280G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[黑色280G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[膚色380G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>裸感厚絨光腿褲襪[黑色380G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[冰川藍L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[冰川藍M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[冰川藍S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[冰川藍XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[夜空藍L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[夜空藍M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[夜空藍S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[夜空藍XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[星耀黑L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[星耀黑M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[星耀黑S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[星耀黑XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[淺花灰L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -16843,7 +16843,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[淺花灰M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[淺花灰S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[淺花灰XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[炭灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[炭灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[炭灰色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -17005,7 +17005,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[炭灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[草木綠L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[草木綠M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -17086,7 +17086,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[草木綠S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>居家棉質男士四角內褲[草木綠XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>洗臉髮帶腕帶三件組[可可棕F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -17243,7 +17243,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>洗臉髮帶腕帶三件組[奶油白F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>洗臉髮帶腕帶三件組[嬰兒藍F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -17297,7 +17297,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>洗臉髮帶腕帶三件組[櫻花粉F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>洗臉髮帶腕帶三件組[雲朵灰F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>洗臉髮帶腕帶三件組[黑色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>舒適鬆緊腰天絲牛仔寬褲[【四季薄款】嬌小款-復古藍L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -17500,7 +17500,7 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>舒適鬆緊腰天絲牛仔寬褲[【秋冬刷毛款】嬌小款-復古藍L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -17527,7 +17527,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>舒適鬆緊腰天絲牛仔寬褲[【秋冬刷毛款】嬌小款-復古藍M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>舒適鬆緊腰天絲牛仔寬褲[【秋冬刷毛款】嬌小款-黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>小巧便攜隨身化妝補妝包[燕麥色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>小巧便攜隨身化妝補妝包[燕麥色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -17749,7 +17749,7 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>小巧便攜隨身化妝補妝包[藍灰色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[深湖藍XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[白色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -17941,7 +17941,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[磚紅色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[花灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[花灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[花灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
@@ -18160,7 +18160,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>莫代爾男士柔感內衣[黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -18233,7 +18233,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】淺卡其S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -18260,7 +18260,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】淺卡其XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -18395,7 +18395,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】白色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -18476,7 +18476,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】粉色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】粉色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】粉色S]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -18557,7 +18557,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】霧藍M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -18611,7 +18611,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【圓領】黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -18638,7 +18638,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【立領】黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
@@ -18719,7 +18719,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
@@ -18773,7 +18773,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>莫代爾長袖打底上衣[【高領】黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>柔軟針織三角披肩[亞麻棕]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -19116,7 +19116,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>柔軟針織三角披肩[卡其色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -19143,7 +19143,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>柔軟針織三角披肩[深灰色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -19170,7 +19170,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>柔軟針織三角披肩[米白色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>柔軟針織三角披肩[酒紅色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -19224,7 +19224,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>柔軟針織三角披肩[黑色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>軟Q寬鬆針織長袖毛衣+短褲套裝[花灰色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>柔軟高腰A字長裙[奶咖色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>柔軟高腰A字長裙[奶咖色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>柔軟高腰A字長裙[深灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -19359,7 +19359,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>柔軟高腰A字長裙[燕麥白L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -19386,7 +19386,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>柔軟高腰A字長裙[燕麥白M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>柔軟高腰A字長裙[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>柔軟高腰A字長裙[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -19486,7 +19486,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>萌萌溫暖毛絨絨長睡裙[深灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>萌萌溫暖毛絨絨長睡裙[皮粉色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -19597,7 +19597,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>針織A字傘狀糯米裙[白杏色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>針織A字傘狀糯米裙[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
@@ -19689,7 +19689,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>重磅數純棉男寬鬆短袖素TEE[夜藍色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>重磅數純棉男寬鬆短袖素TEE[橄欖綠L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>重磅數純棉男寬鬆短袖素TEE[橄欖綠XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>重磅數純棉男寬鬆短袖素TEE[煤灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>重磅數純棉男寬鬆短袖素TEE[煤灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>重磅數純棉男寬鬆短袖素TEE[燕麥白L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>重磅數純棉男寬鬆短袖素TEE[燕麥白M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>重磅數純棉男寬鬆短袖素TEE[石墨黑L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -20000,7 +20000,7 @@
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>重磅數純棉男寬鬆短袖素TEE[石墨黑M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -20027,7 +20027,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>重磅數純棉男寬鬆短袖素TEE[石墨黑XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -20054,7 +20054,7 @@
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>重磅數純棉男寬鬆短袖素TEE[純白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>重磅數純棉男士休閒五分短褲[卡其色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>重磅數純棉男士休閒五分短褲[黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【中號】花朵]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -20352,7 +20352,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【內衣用】花朵]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【加大】花朵]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【圓柱】花朵]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【大號】花朵]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【小號】花朵]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -20487,7 +20487,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【迷你】花朵]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【中號】銀杏]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -20560,7 +20560,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【內衣用】銀杏]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【加大】銀杏]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【圓柱】銀杏]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -20641,7 +20641,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【大號】銀杏]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【小號】銀杏]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>洗衣機專用細網洗衣袋[【迷你】銀杏]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -20960,7 +20960,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[珊瑚粉L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[珊瑚粉M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[珊瑚粉XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
@@ -21041,7 +21041,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -21068,7 +21068,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -21095,7 +21095,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -21122,7 +21122,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[豆沙紅L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[豆沙紅M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[豆沙紅XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -21257,7 +21257,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -21311,7 +21311,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -21365,7 +21365,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[藏青色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[藏青色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[藏青色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -21554,7 +21554,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -21581,7 +21581,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -21608,7 +21608,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>零感無暇雙層校色光腿褲襪[中膚色140G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>零感無暇雙層校色光腿褲襪[中膚色180G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>零感無暇雙層校色光腿褲襪[深膚色140G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
@@ -21689,7 +21689,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>零感無暇雙層校色光腿褲襪[深膚色180G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>零感無暇雙層校色光腿褲襪[淺膚色140G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
@@ -21743,7 +21743,7 @@
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>零感無暇雙層校色光腿褲襪[淺膚色180G]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -21770,7 +21770,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>零食封口防潮密封夾[白色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
@@ -21797,7 +21797,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>零食封口防潮密封夾[紅色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>零食封口防潮密封夾[綠色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>零食封口防潮密封夾[黃色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -21878,7 +21878,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>可愛小動物雙層手機包[動物派對]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
@@ -21905,7 +21905,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>可愛小動物雙層手機包[湖綠大貓]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>可愛小動物雙層手機包[白色熊熊]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>可愛小動物雙層手機包[白色鳥語]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -22005,7 +22005,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>可愛小動物雙層小零錢包[動物派對]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -22070,7 +22070,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>可愛小動物雙層小零錢包[白色貓咪]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>可愛小動物雙層小零錢包[白色鳥語]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>可愛小動物雙層小零錢包[粉紅小兔]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>可愛小動物雙層小零錢包[紅色柴犬]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -22178,7 +22178,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>可愛小動物雙層小零錢包[黃色小鴨]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>可愛小動物雙層小零錢包[黑色格紋]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -22232,7 +22232,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>韓系素色五分袖中長版T恤裙[咖啡色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -22259,7 +22259,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>韓系素色五分袖中長版T恤裙[白色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>韓系素色五分袖中長版T恤裙[黑色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -22332,7 +22332,7 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[摩卡色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[摩卡色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -22386,7 +22386,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[摩卡色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -22413,7 +22413,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
@@ -22494,7 +22494,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[煙粉色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -22521,7 +22521,7 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[煙粉色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[煙粉色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[米咖色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[米咖色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[米咖色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -22656,7 +22656,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -22791,7 +22791,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[黑色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】原味]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】桂花]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】海燕窩]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
@@ -23051,7 +23051,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】玫瑰四物]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】紅棗桂圓]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>罐裝.ᐟ臺灣天然手工黑糖[【罐裝400G】老薑]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -23132,7 +23132,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>短版薄款圓領T恤[【基本款】湖藍色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>短版薄款圓領T恤[【基本款】灰色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
@@ -23224,7 +23224,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>短版薄款圓領T恤[【基本款】黑色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>日系尺碼標高質感內褲包裝袋[L碼]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>韓小清新微捲邊中筒襪[奶油黃]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>韓小清新微捲邊中筒襪[淺杏桃]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -23484,7 +23484,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>韓小清新微捲邊中筒襪[燕麥色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -23511,7 +23511,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>韓小清新微捲邊中筒襪[玫粉色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -23538,7 +23538,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>韓小清新微捲邊中筒襪[純白色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D956" t="inlineStr">
@@ -23565,7 +23565,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>韓小清新微捲邊中筒襪[純黑色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -23592,7 +23592,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>韓小清新微捲邊中筒襪[薑黃色]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
@@ -23619,7 +23619,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>連帽寬鬆長版帽T裙[咖啡色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
@@ -23646,7 +23646,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>連帽寬鬆長版帽T裙[深藍色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -23673,7 +23673,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>連帽寬鬆長版帽T裙[淺灰色F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
@@ -23700,7 +23700,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>寬鬆薄絨條紋長版長袖連身裙[白條紋F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -23727,7 +23727,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>寬鬆薄絨條紋長版長袖連身裙[黑條紋F]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
@@ -23811,7 +23811,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>薄款復古風寬鬆長袖上衣[碳灰色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
@@ -23876,7 +23876,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>薄款復古風寬鬆長袖上衣[雲灰白XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -24093,7 +24093,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
@@ -24147,7 +24147,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[寶藍色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -24201,7 +24201,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
@@ -24255,7 +24255,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
@@ -24309,7 +24309,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
@@ -24363,7 +24363,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
@@ -24390,7 +24390,7 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>素色冰絲女士三角內褲[白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -24525,7 +24525,7 @@
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[煙粉色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[米咖色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -24579,7 +24579,7 @@
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
@@ -24633,7 +24633,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
@@ -24687,7 +24687,7 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[白色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
@@ -24714,7 +24714,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[酒紅色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
@@ -24768,7 +24768,7 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>街頭風NO字母五分袖T恤裙[灰色F]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>IKEA 正版環保購物袋[【手提款】71L]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】灰色L]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色L]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色M]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色S]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】白色L]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】粉色L]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】霧藍L]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】黑色L]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色L]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色M]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色L]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色S]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色XL]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣美肌超薄透膚絲襪[基本黑]</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣美肌超薄透膚絲襪[白皙膚]</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣美肌超薄透膚絲襪[自然膚]</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[丁香紫L]</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[丁香紫M]</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[丁香紫XL]</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[中豆紅L]</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[中豆紅M]</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[中豆紅XL]</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[白色L]</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[白色M]</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[白色XL]</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[膚色L]</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[膚色M]</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[膚色XL]</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[藍灰色L]</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[藍灰色M]</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[藍灰色XL]</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[黑色L]</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[黑色M]</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[黑色XL]</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色莫代爾V領短袖T[黑色L]</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>筆筒文具多功能桌面收纳盒[粉色]</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>筆筒文具多功能桌面收纳盒[藍色]</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[原味【單顆】18g]</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[桂圓紅棗【單顆】18g]</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[桂花【單顆】18g]</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[海燕窩【單顆】18g]</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[玫瑰四物【單顆】18g]</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[老薑【單顆】18g]</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>毛呢舒適鬆緊腰百褶短裙[咖啡色XL]</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>毛呢舒適鬆緊腰百褶短裙[深灰色L]</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>毛呢舒適鬆緊腰百褶短裙[深灰色M]</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>毛呢舒適鬆緊腰百褶短裙[深灰色XL]</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>毛呢舒適鬆緊腰百褶短裙[米白色L]</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>毛呢舒適鬆緊腰百褶短裙[米白色XL]</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色M]</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色S]</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色M]</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色S]</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色XL]</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[灰色L]</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[灰色S]</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[白色M]</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[白色S]</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[白色XL]</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[紫色L]</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[紫色M]</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[紫色S]</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色S]</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色L]</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色M]</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[黑色S]</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[黑色XL]</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製冰絲涼感防曬袖套[【平口款】深灰色F]</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製冰絲涼感防曬袖套[【平口款】深藍色F]</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製冰絲涼感防曬袖套[【平口款】黑色F]</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製冰絲涼感防曬袖套[【露指款】深灰色F]</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製冰絲涼感防曬袖套[【露指款】深藍色F]</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製冰絲涼感防曬袖套[【露指款】黑色F]</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製強力高彈輕量褲襪[亮膚色140G]</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製強力高彈輕量褲襪[亮膚色30G]</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製強力高彈輕量褲襪[亮膚色50G]</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製強力高彈輕量褲襪[深膚色140G]</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製強力高彈輕量褲襪[深膚色30G]</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製強力高彈輕量褲襪[深膚色50G]</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製強力高彈輕量褲襪[黑色140G]</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製強力高彈輕量褲襪[黑色30G]</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>台灣製強力高彈輕量褲襪[黑色50G]</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/中長/灰色L]</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/中長/灰色M]</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/中長/灰色XL]</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/加長/灰色XL]</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/短版/灰色L]</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/短版/灰色M]</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/短版/灰色XL]</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/中長/白色L]</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/中長/白色M]</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/中長/白色XL]</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/加長/白色L]</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/加長/白色XL]</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/短版/白色L]</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/短版/白色M]</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/短版/白色XL]</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/中長/黑色L]</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/中長/黑色XL]</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/加長/黑色L]</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/加長/黑色XL]</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/短版/黑色L]</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/短版/黑色M]</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[吊帶款/短版/黑色XL]</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/中長/灰色L]</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/中長/灰色M]</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/中長/灰色XL]</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/短版/灰色M]</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/短版/灰色XL]</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/中長/白色L]</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/中長/白色M]</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/中長/白色XL]</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/短版/白色L]</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/短版/白色M]</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/短版/白色XL]</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/中長/黑色L]</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/中長/黑色M]</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/中長/黑色XL]</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/短版/黑色L]</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/短版/黑色M]</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾打底連身裙[背心款/短版/黑色XL]</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>大容量PVC防水收納包[【拉鍊款】米白色]</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[原味【罐裝】400g]</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[桂花【罐裝】400g]</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[海燕窩【罐裝】400g]</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[玫瑰四物【罐裝】400g]</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[紅棗桂圓【罐裝】400g]</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[老薑【罐裝】400g]</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【中領】月光灰L]</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【中領】月光灰S]</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【中領】月光灰XL]</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【圓領】月光灰L]</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【圓領】月光灰M]</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【圓領】月光灰XL]</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【中領】珊瑚粉M]</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【中領】珊瑚粉XL]</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【圓領】珊瑚粉M]</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【圓領】珊瑚粉S]</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【中領】神秘黑L]</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【中領】神秘黑M]</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【中領】神秘黑S]</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【中領】神秘黑XL]</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【圓領】神秘黑L]</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【圓領】神秘黑S]</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【圓領】神秘黑XL]</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【中領】經典膚S]</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【中領】經典膚XL]</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【圓領】經典膚L]</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>德絨保暖打底長袖上衣[【圓領】經典膚M]</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[沙粉色M]</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[黑色M]</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[黑色S]</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【細肩帶】白色L]</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【細肩帶】白色M]</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【細肩帶】膚色L]</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【細肩帶】膚色M]</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【細肩帶】黑色L]</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【細肩帶】黑色M]</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【寬肩帶】灰色L]</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【寬肩帶】白色L]</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【寬肩帶】白色M]</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【寬肩帶】膚色L]</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【寬肩帶】黑色L]</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>輕薄莫代爾打底背心[【寬肩帶】黑色M]</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超防掉隱形PRO無肩帶內衣[乳白色L]</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超防掉隱形PRO無肩帶內衣[乳白色S]</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超防掉隱形PRO無肩帶內衣[優雅黑L]</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超防掉隱形PRO無肩帶內衣[粉底膚S]</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[冰川白L]</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[冰川白M]</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[奶咖色L]</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[奶咖色M]</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[奶咖色XL]</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[奶油黃L]</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[奶油黃M]</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[奶油黃XL]</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[薄荷綠L]</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[薄荷綠M]</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[薄荷綠XL]</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[輕氧藍L]</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[輕氧藍M]</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[輕氧藍XL]</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[雅黑色L]</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[雅黑色M]</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>冰絲面膜速乾三角內褲[雅黑色XL]</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>黑繃帶高腰收腹三角內褲[楓木色F]</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>黑繃帶高腰收腹三角內褲[綠蘿紗F]</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>黑繃帶高腰收腹三角內褲[綠蘿紗XL]</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>黑繃帶高腰收腹三角內褲[羊毛色F]</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>黑繃帶高腰收腹三角內褲[羊毛色XL]</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>黑繃帶高腰收腹三角內褲[肉桂粉F]</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>黑繃帶高腰收腹三角內褲[肉桂粉XL]</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>黑繃帶高腰收腹三角內褲[黑色F]</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色L]</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色M]</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色S]</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】深藍色XL]</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】淺灰色L]</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】淺灰色M]</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】淺灰色S]</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】淺灰色XL]</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】淺綠色L]</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】淺綠色M]</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】淺綠色S]</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】淺綠色XL]</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色L]</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色M]</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色S]</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色L]</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色M]</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色S]</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】深藍色XL]</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】淺灰色L]</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】淺灰色M]</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】淺灰色S]</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】淺灰色XL]</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色L]</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色M]</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色S]</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】淺藍色XL]</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】黑灰色L]</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】黑灰色M]</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】黑灰色S]</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【條紋】黑灰色XL]</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[2倍厚A]</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[2倍厚B]</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[2倍厚C]</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[2倍厚D]</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[4倍厚A]</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[4倍厚B]</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[4倍厚C]</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[4倍厚D]</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[立體杯A]</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[立體杯B]</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[立體杯C]</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>水感矽膠隱形胸罩[立體杯D]</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>可愛動物眼鏡墨鏡保護收納掛袋[棕色小熊]</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>可愛動物眼鏡墨鏡保護收納掛袋[灰白小貓]</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>可愛動物眼鏡墨鏡保護收納掛袋[黃白小貓]</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>日式可摺疊式輕量保溫便當袋[可可棕]</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>日式可摺疊式輕量保溫便當袋[大象灰]</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>站立式化妝刷具旅行收納包[卡其色]</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>旅行衣物分裝收納整理袋[米色]</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>旅行衣物分裝收納整理袋[粉色]</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>旅行衣物分裝收納整理袋[藍色]</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>旅行衣物分裝收納整理袋[黑色]</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>分層萬用小物收納網格袋[燕麥色L]</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -10810,7 +10810,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>分層萬用小物收納網格袋[燕麥色M]</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>分層萬用小物收納網格袋[燕麥色S]</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>分層萬用小物收納網格袋[藍灰色M]</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>分層萬用小物收納網格袋[藍灰色S]</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>旅行摺疊衣架夾[碧波紋]</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>隱形不透款無痕內衣[【寬肩帶】深膚色F]</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>隱形不透款無痕內衣[【寬肩帶】深膚色XXL]</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>隱形不透款無痕內衣[【細肩帶】抹茶綠XXL]</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>隱形不透款無痕內衣[【細肩帶】淺膚色XXL]</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】淺卡其L]</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】淺卡其M]</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】淺卡其XL]</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】淺卡其M]</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】淺卡其M]</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】淺卡其XL]</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】灰色L]</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】灰色S]</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】灰色XL]</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】灰色L]</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】灰色M]</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】灰色S]</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】灰色L]</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】灰色M]</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】白色L]</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】白色M]</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】白色S]</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】白色XL]</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色L]</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色M]</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色S]</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色XL]</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】白色L]</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】白色M]</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】白色XL]</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】粉色L]</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】粉色S]</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】粉色XL]</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】粉色XL]</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】粉色M]</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】粉色XL]</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】霧藍L]</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】霧藍XL]</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】霧藍L]</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】霧藍S]</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】霧藍XL]</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】霧藍M]</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】霧藍XL]</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】黑色L]</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】黑色M]</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】黑色S]</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】黑色XL]</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色L]</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色M]</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色S]</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色XL]</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色L]</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色M]</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色S]</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色XL]</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>羅紋長袖打底上衣[咖啡色M]</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>羅紋長袖打底上衣[灰色M]</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>羅紋長袖打底上衣[灰色XL]</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>羅紋長袖打底上衣[白色M]</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>羅紋長袖打底上衣[白色XL]</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>羅紋長袖打底上衣[薄荷綠M]</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>羅紋長袖打底上衣[黑色L]</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>羅紋長袖打底上衣[黑色M]</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>羅紋長袖打底上衣[黑色XL]</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】淺卡其L]</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】灰色XL]</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】白色XL]</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色L]</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色S]</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -14822,7 +14822,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色XL]</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】白色L]</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】白色XL]</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】粉色L]</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】霧藍XL]</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -14957,7 +14957,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】霧藍XL]</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】霧藍M]</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】黑色M]</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】黑色XL]</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -15065,7 +15065,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色L]</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色M]</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色XL]</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色L]</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色M]</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色XL]</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[沙粉色L]</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[沙粉色M]</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[沙粉色S]</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[沙粉色XL]</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[深岩灰L]</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[深岩灰M]</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[深岩灰XL]</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[深海藍L]</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[深海藍S]</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[深海藍XL]</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[白色L]</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[白色M]</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[白色S]</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[麻灰色L]</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[麻灰色M]</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[麻灰色S]</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[麻灰色XL]</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[黑色L]</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[黑色M]</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[黑色S]</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>男女圓領寬鬆素色長袖大學TEE[黑色XL]</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[膚色140G]</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[黑色140G]</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[膚色180G]</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[黑色180G]</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[膚色280G]</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[黑色280G]</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[膚色380G]</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[黑色380G]</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[膚色140G]</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[黑色140G]</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[膚色180G]</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[黑色180G]</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[膚色280G]</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[黑色280G]</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[膚色380G]</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>裸感厚絨光腿褲襪[黑色380G]</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[冰川藍L]</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[冰川藍M]</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[冰川藍S]</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[冰川藍XL]</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[夜空藍L]</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[夜空藍M]</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[夜空藍S]</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[夜空藍XL]</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[星耀黑L]</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[星耀黑M]</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[星耀黑S]</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[星耀黑XL]</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[淺花灰L]</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -16843,7 +16843,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[淺花灰M]</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[淺花灰S]</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[淺花灰XL]</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[炭灰色L]</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[炭灰色M]</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[炭灰色S]</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -17005,7 +17005,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[炭灰色XL]</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[草木綠L]</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[草木綠M]</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -17086,7 +17086,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[草木綠S]</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[草木綠XL]</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗臉髮帶腕帶三件組[可可棕]</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -17243,7 +17243,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗臉髮帶腕帶三件組[奶白色]</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗臉髮帶腕帶三件組[嬰兒藍]</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -17297,7 +17297,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗臉髮帶腕帶三件組[櫻花粉]</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗臉髮帶腕帶三件組[雲朵灰]</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗臉髮帶腕帶三件組[黑色]</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[深湖藍XL]</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[白色L]</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[白色M]</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[白色S]</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -17941,7 +17941,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[白色XL]</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[磚紅色XL]</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[花灰色L]</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[花灰色M]</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[花灰色XL]</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[黑色L]</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
@@ -18160,7 +18160,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[黑色M]</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾男士柔感內衣[黑色XL]</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -18233,7 +18233,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】淺卡其S]</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -18260,7 +18260,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】淺卡其XL]</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】灰色M]</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】灰色L]</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】灰色M]</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】灰色XL]</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -18395,7 +18395,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色M]</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】白色S]</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】白色M]</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -18476,7 +18476,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】粉色S]</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】粉色L]</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】粉色S]</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -18557,7 +18557,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】霧藍M]</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】黑色L]</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -18611,7 +18611,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】黑色XL]</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -18638,7 +18638,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色L]</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色M]</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【立領】黑色XL]</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
@@ -18719,7 +18719,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色L]</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色M]</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
@@ -18773,7 +18773,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】黑色XL]</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟針織三角披肩[亞麻棕]</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -19116,7 +19116,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟針織三角披肩[卡其色]</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -19143,7 +19143,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟針織三角披肩[深灰色]</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -19170,7 +19170,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟針織三角披肩[米白色]</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟針織三角披肩[酒紅色]</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -19224,7 +19224,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟針織三角披肩[黑色]</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>軟Q寬鬆針織長袖毛衣+短褲套裝[花灰色F]</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟高腰A字長裙[奶咖色L]</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟高腰A字長裙[奶咖色M]</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -19359,7 +19359,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟高腰A字長裙[燕麥白L]</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -19386,7 +19386,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟高腰A字長裙[燕麥白M]</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟高腰A字長裙[黑色L]</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔軟高腰A字長裙[黑色M]</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -19689,7 +19689,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男寬鬆短袖素TEE[夜藍色XL]</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男寬鬆短袖素TEE[橄欖綠L]</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男寬鬆短袖素TEE[橄欖綠XL]</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男寬鬆短袖素TEE[煤灰色L]</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男寬鬆短袖素TEE[煤灰色XL]</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男寬鬆短袖素TEE[燕麥白L]</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男寬鬆短袖素TEE[燕麥白M]</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男寬鬆短袖素TEE[石墨黑L]</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -20000,7 +20000,7 @@
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男寬鬆短袖素TEE[石墨黑M]</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -20027,7 +20027,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男寬鬆短袖素TEE[石墨黑XL]</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -20054,7 +20054,7 @@
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男寬鬆短袖素TEE[純白色L]</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男士休閒五分短褲[卡其色L]</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>重磅數純棉男士休閒五分短褲[黑色XL]</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【中號】花朵]</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -20352,7 +20352,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【內衣用】花朵]</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【加大】花朵]</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【圓柱】花朵]</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【大號】花朵]</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【小號】花朵]</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -20487,7 +20487,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【迷你】花朵]</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【中號】銀杏]</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -20560,7 +20560,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【內衣用】銀杏]</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【加大】銀杏]</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【圓柱】銀杏]</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -20641,7 +20641,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【大號】銀杏]</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【小號】銀杏]</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>洗衣機專用細網洗衣袋[【迷你】銀杏]</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[灰色L]</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[灰色M]</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[灰色XL]</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -20960,7 +20960,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[珊瑚粉L]</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[珊瑚粉M]</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[珊瑚粉XL]</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
@@ -21041,7 +21041,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[白色L]</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -21068,7 +21068,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[白色M]</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -21095,7 +21095,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[白色XL]</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -21122,7 +21122,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[豆沙紅L]</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[豆沙紅M]</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[豆沙紅XL]</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[黑色L]</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[黑色M]</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -21257,7 +21257,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（女款）超暖雙面絨發熱衣+發熱褲套裝[黑色XL]</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[灰色L]</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -21311,7 +21311,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[灰色M]</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[灰色XL]</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -21365,7 +21365,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[白色L]</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[白色M]</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[白色XL]</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[藏青色L]</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[藏青色M]</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[藏青色XL]</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[黑色L]</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -21554,7 +21554,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[黑色M]</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -21581,7 +21581,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>（男款）超暖雙面絨發熱衣+發熱褲套裝[黑色XL]</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -21608,7 +21608,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>零感無暇雙層校色光腿褲襪[中膚色140G]</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>零感無暇雙層校色光腿褲襪[中膚色180G]</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>零感無暇雙層校色光腿褲襪[深膚色140G]</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
@@ -21689,7 +21689,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>零感無暇雙層校色光腿褲襪[深膚色180G]</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>零感無暇雙層校色光腿褲襪[淺膚色140G]</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
@@ -21743,7 +21743,7 @@
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>零感無暇雙層校色光腿褲襪[淺膚色180G]</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -21878,7 +21878,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>可愛小動物雙層手機包[湖綠大貓]</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
@@ -21905,7 +21905,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>可愛小動物雙層手機包[紅色柴犬]</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>可愛小動物雙層手機包[白色熊熊]</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>可愛小動物雙層手機包[白色鳥語]</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -22005,7 +22005,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>防水牛津布雙層小零錢包[動物派對]</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -22070,7 +22070,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>防水牛津布雙層小零錢包[白色貓咪]</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>防水牛津布雙層小零錢包[白色鳥語]</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>防水牛津布雙層小零錢包[粉色小兔]</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>防水牛津布雙層小零錢包[紅色柴犬]</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -22178,7 +22178,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>防水牛津布雙層小零錢包[黃色小鴨]</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>防水牛津布雙層小零錢包[黑色格紋]</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -22232,7 +22232,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>韓系素色五分袖中長版T恤裙[咖啡色F]</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -22259,7 +22259,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>韓系素色五分袖中長版T恤裙[白色F]</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>韓系素色五分袖中長版T恤裙[黑色F]</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -22332,7 +22332,7 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[摩卡色L]</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[摩卡色M]</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -22386,7 +22386,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[摩卡色XL]</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -22413,7 +22413,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠L]</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M]</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠XL]</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
@@ -22494,7 +22494,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[煙粉色L]</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -22521,7 +22521,7 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[煙粉色M]</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[煙粉色XL]</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[米咖色L]</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[米咖色M]</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[米咖色XL]</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -22656,7 +22656,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭L]</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭M]</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭XL]</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[黑色L]</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[黑色M]</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -22791,7 +22791,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[黑色XL]</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[原味【罐裝】400g]</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[桂花【罐裝】400g]</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[海燕窩【罐裝】400g]</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
@@ -23051,7 +23051,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[玫瑰四物【罐裝】400g]</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[紅棗桂圓【罐裝】400g]</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>罐裝.ᐟ臺灣天然手工黑糖[老薑【罐裝】400g]</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -23132,7 +23132,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>短版薄款圓領T恤[【基本款】湖藍色F]</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>短版薄款圓領T恤[【基本款】灰色F]</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
@@ -23224,7 +23224,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>短版薄款圓領T恤[【基本款】黑色F]</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>日系尺碼標高質感內褲包裝袋[L碼]</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>韓小清新微捲邊中筒襪[奶油黃]</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>韓小清新微捲邊中筒襪[淺杏桃]</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -23484,7 +23484,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>韓小清新微捲邊中筒襪[燕麥色]</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -23511,7 +23511,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>韓小清新微捲邊中筒襪[玫粉色]</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -23538,7 +23538,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>韓小清新微捲邊中筒襪[純白色]</t>
         </is>
       </c>
       <c r="D956" t="inlineStr">
@@ -23565,7 +23565,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>韓小清新微捲邊中筒襪[純黑色]</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -23592,7 +23592,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>韓小清新微捲邊中筒襪[薑黃色]</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
@@ -23619,7 +23619,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>連帽寬鬆長版帽T裙[咖啡色F]</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
@@ -23646,7 +23646,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>連帽寬鬆長版帽T裙[深藍色F]</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -23673,7 +23673,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>連帽寬鬆長版帽T裙[淺灰色F]</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
@@ -23700,7 +23700,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>寬鬆薄絨條紋長版長袖連身裙[白條紋F]</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -23727,7 +23727,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>寬鬆薄絨條紋長版長袖連身裙[黑條紋F]</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
@@ -23811,7 +23811,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>薄款復古風寬鬆長袖上衣[碳灰色L]</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
@@ -23876,7 +23876,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>薄款復古風寬鬆長袖上衣[雲灰白XL]</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -24093,7 +24093,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色L]</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[咖啡色XL]</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
@@ -24147,7 +24147,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色L]</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[寶藍色XL]</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -24201,7 +24201,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[灰色XL]</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
@@ -24255,7 +24255,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[白色XL]</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[紫色XL]</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
@@ -24309,7 +24309,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色XL]</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
@@ -24363,7 +24363,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色XL]</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
@@ -24390,7 +24390,7 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>素色冰絲女士三角內褲[白色L]</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[灰湖綠M]</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -24525,7 +24525,7 @@
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[煙粉色M]</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[米咖色M]</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -24579,7 +24579,7 @@
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>舒適寬邊莫代爾女士三角內褲[紫羅蘭M]</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>柔順莫代爾男士四角內褲[【素色】黑灰色XL]</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
@@ -24633,7 +24633,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[灰色M]</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[白色L]</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
@@ -24687,7 +24687,7 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[白色M]</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
@@ -24714,7 +24714,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色M]</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[酒紅色M]</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
@@ -24768,7 +24768,7 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[黑色L]</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[黑色M]</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -11970,7 +11970,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>居家棉質男士四角內褲[炭灰色XL]</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -11931,7 +11931,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>新款PU皮立式化妝刷具旅行收納包[白蛋色]</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>新款PU皮立式化妝刷具旅行收納包[霧玫瑰]</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -22488,7 +22488,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:YGJ03002-OR×30 + YGK03002-PK×1</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -22542,7 +22542,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:YGJ03002-OG×30 + YGK03002-RR×1</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:YGJ03002-OG×30 + YGK03002-CG×1</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:YGJ03002-OG×30 + YGK03002-CG×1</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -23811,7 +23811,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:YGJ03002-OG×30</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -25566,11 +25566,19 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>未匹配</t>
-        </is>
-      </c>
-      <c r="D932" t="inlineStr"/>
-      <c r="E932" t="inlineStr"/>
+          <t>莫代爾打底連身裙[吊帶款/中長/白色L]</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-MD-WH-L</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -25585,11 +25593,19 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>未匹配</t>
-        </is>
-      </c>
-      <c r="D933" t="inlineStr"/>
-      <c r="E933" t="inlineStr"/>
+          <t>莫代爾打底連身裙[吊帶款/加長/白色L]</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-LG-WH-L</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -25620,12 +25620,12 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【圓領】白色L]</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>HFA02001-WH_CN-L</t>
+          <t>HFA02001-CN-WH-L</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -25647,12 +25647,12 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>莫代爾長袖打底上衣[【高領】白色L]</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>HFA02001-WH_TN-L</t>
+          <t>HFA02001-TN-WH-L</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -39645,7 +39645,7 @@
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:YGK03002-RR×1</t>
         </is>
       </c>
       <c r="D1453" t="inlineStr">
@@ -39672,7 +39672,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>組合:YGK03002-RR×1</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
@@ -39988,17 +39988,17 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>日系尺碼標高質感內褲包裝袋[L碼]</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr">
         <is>
-          <t>HGK03001B-L</t>
+          <t>HGK03001-L</t>
         </is>
       </c>
       <c r="E1466" t="inlineStr">
         <is>
-          <t>HGK03001B</t>
+          <t>HGK03001</t>
         </is>
       </c>
     </row>
@@ -40069,17 +40069,17 @@
       </c>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>日系尺碼標高質感內褲包裝袋[XL碼]</t>
         </is>
       </c>
       <c r="D1469" t="inlineStr">
         <is>
-          <t>HGK03001B-XL</t>
+          <t>HGK03001-XL</t>
         </is>
       </c>
       <c r="E1469" t="inlineStr">
         <is>
-          <t>HGK03001B</t>
+          <t>HGK03001</t>
         </is>
       </c>
     </row>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -58240,17 +58240,17 @@
       </c>
       <c r="C2142" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[灰色L]</t>
         </is>
       </c>
       <c r="D2142" t="inlineStr">
         <is>
-          <t>TB300001-灰色-L-新標</t>
+          <t>HME03001-GY-L</t>
         </is>
       </c>
       <c r="E2142" t="inlineStr">
         <is>
-          <t>TB300001</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
@@ -58456,17 +58456,17 @@
       </c>
       <c r="C2150" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>超薄裸感冰絲男士四角內褲[藏藍色L]</t>
         </is>
       </c>
       <c r="D2150" t="inlineStr">
         <is>
-          <t>TB300001-藏藍色-L-新標</t>
+          <t>HME03001-DN-L</t>
         </is>
       </c>
       <c r="E2150" t="inlineStr">
         <is>
-          <t>TB300001</t>
+          <t>HME03001</t>
         </is>
       </c>
     </row>

--- a/data/對照表.xlsx
+++ b/data/對照表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2164"/>
+  <dimension ref="A1:E2165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20988,12 +20988,12 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>分層萬用小物收納網格袋[藍灰色M]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>HGI03010-BLG-M</t>
+          <t>HGI03010-BU-M</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
@@ -32760,17 +32760,17 @@
       </c>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>柔軟高腰A字長裙[黑色L]</t>
+          <t>未匹配</t>
         </is>
       </c>
       <c r="D1198" t="inlineStr">
         <is>
-          <t>HFB02004-BK-L</t>
+          <t>HFB02003-BK-L</t>
         </is>
       </c>
       <c r="E1198" t="inlineStr">
         <is>
-          <t>HFB02004</t>
+          <t>HFB02003</t>
         </is>
       </c>
     </row>
@@ -56296,12 +56296,12 @@
       </c>
       <c r="C2070" t="inlineStr">
         <is>
-          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】桂圓紅棗]</t>
+          <t>單顆入.ᐟ台灣手工黑糖塊[【單顆18G】玫瑰四物]</t>
         </is>
       </c>
       <c r="D2070" t="inlineStr">
         <is>
-          <t>YGJ03002-RDL</t>
+          <t>YGJ03002-RFH</t>
         </is>
       </c>
       <c r="E2070" t="inlineStr">
@@ -58845,6 +58845,33 @@
       <c r="E2164" t="inlineStr">
         <is>
           <t>HFF02002</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>HME03001-CUS</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲[CUS]</t>
+        </is>
+      </c>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>HME03001-CUS</t>
+        </is>
+      </c>
+      <c r="E2165" t="inlineStr">
+        <is>
+          <t>HME03001</t>
         </is>
       </c>
     </row>
